--- a/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_30_49.xlsx
+++ b/model/Outputs/11. Interest rate/20/Output Files/0.1/Output_30_49.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5779083.817078358</v>
+        <v>5779120.075560286</v>
       </c>
     </row>
     <row r="7">
@@ -526,7 +526,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4937391.165086121</v>
+        <v>4937391.16508612</v>
       </c>
     </row>
     <row r="10">
@@ -536,7 +536,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4937391.165086121</v>
+        <v>4937391.16508612</v>
       </c>
     </row>
     <row r="11">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>32524258.28764697</v>
+        <v>32524258.28764698</v>
       </c>
     </row>
   </sheetData>
@@ -945,10 +945,10 @@
         <v>0</v>
       </c>
       <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
         <v>111.8616000000015</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>127.0000000000001</v>
@@ -1082,19 +1082,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>55.16107041894321</v>
+        <v>0</v>
       </c>
       <c r="N7" t="n">
-        <v>107.1999441241438</v>
+        <v>0</v>
       </c>
       <c r="O7" t="n">
-        <v>76.50058545691995</v>
+        <v>111.8616000000069</v>
       </c>
       <c r="P7" t="n">
         <v>127.0000000000001</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>127.0000000000001</v>
       </c>
       <c r="R7" t="n">
         <v>127.0000000000001</v>
@@ -1182,10 +1182,10 @@
         <v>0</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>123.3120000000028</v>
       </c>
       <c r="U8" t="n">
-        <v>123.3120000000028</v>
+        <v>0</v>
       </c>
       <c r="V8" t="n">
         <v>140.0000000000001</v>
@@ -1319,13 +1319,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>53.16107041894242</v>
+        <v>18.11205587586694</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>105.199944124143</v>
       </c>
       <c r="O10" t="n">
-        <v>70.15092958106752</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
         <v>140.0000000000001</v>
@@ -1422,7 +1422,7 @@
         <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>144.4512000000021</v>
+        <v>164</v>
       </c>
       <c r="V11" t="n">
         <v>164</v>
@@ -1431,7 +1431,7 @@
         <v>164</v>
       </c>
       <c r="X11" t="n">
-        <v>164</v>
+        <v>144.4512000000021</v>
       </c>
       <c r="Y11" t="n">
         <v>0</v>
@@ -1553,13 +1553,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>24.29789045285913</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>104.7250265656118</v>
       </c>
       <c r="N13" t="n">
-        <v>144.4512000000129</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
         <v>164</v>
@@ -1574,7 +1574,7 @@
         <v>164</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>15.42828298154197</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -1656,7 +1656,7 @@
         <v>0</v>
       </c>
       <c r="T14" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="U14" t="n">
         <v>164</v>
@@ -1665,10 +1665,10 @@
         <v>164</v>
       </c>
       <c r="W14" t="n">
+        <v>164</v>
+      </c>
+      <c r="X14" t="n">
         <v>144.4512000000262</v>
-      </c>
-      <c r="X14" t="n">
-        <v>0</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
@@ -1684,7 +1684,7 @@
         <v>29.55655664632462</v>
       </c>
       <c r="C15" t="n">
-        <v>1.641580692948328</v>
+        <v>6.099912445517305</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -1750,7 +1750,7 @@
         <v>64.86273944538556</v>
       </c>
       <c r="Y15" t="n">
-        <v>44.39139276613236</v>
+        <v>39.93306101356339</v>
       </c>
     </row>
     <row r="16">
@@ -1796,13 +1796,13 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>144.4512000000262</v>
       </c>
       <c r="O16" t="n">
-        <v>144.4512000000262</v>
+        <v>164</v>
       </c>
       <c r="P16" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
         <v>164</v>
@@ -1896,16 +1896,16 @@
         <v>164.0000000000009</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>164.0000000000009</v>
       </c>
       <c r="V17" t="n">
         <v>164.0000000000009</v>
       </c>
       <c r="W17" t="n">
-        <v>164.0000000000009</v>
+        <v>144.4512000000559</v>
       </c>
       <c r="X17" t="n">
-        <v>144.4512000000559</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
         <v>0</v>
@@ -2130,19 +2130,19 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>171.0000000000029</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>171.000000000003</v>
       </c>
       <c r="V20" t="n">
-        <v>171.0000000000029</v>
+        <v>171.000000000003</v>
       </c>
       <c r="W20" t="n">
-        <v>171.0000000000029</v>
+        <v>171.000000000003</v>
       </c>
       <c r="X20" t="n">
-        <v>150.6168000000903</v>
+        <v>150.6168000000905</v>
       </c>
       <c r="Y20" t="n">
         <v>0</v>
@@ -2267,22 +2267,22 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>47.41685587596788</v>
+        <v>47.41685587596811</v>
       </c>
       <c r="N22" t="n">
         <v>103.1999441241422</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>171.000000000003</v>
       </c>
       <c r="P22" t="n">
-        <v>171.0000000000029</v>
+        <v>171.000000000003</v>
       </c>
       <c r="Q22" t="n">
-        <v>171.0000000000029</v>
+        <v>171.000000000003</v>
       </c>
       <c r="R22" t="n">
-        <v>171.0000000000029</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>150.6168000000471</v>
+        <v>171.0000000000056</v>
       </c>
       <c r="V26" t="n">
         <v>171.0000000000056</v>
@@ -2616,7 +2616,7 @@
         <v>171.0000000000056</v>
       </c>
       <c r="X26" t="n">
-        <v>171.0000000000056</v>
+        <v>150.616800000047</v>
       </c>
       <c r="Y26" t="n">
         <v>0</v>
@@ -2644,7 +2644,7 @@
         <v>0</v>
       </c>
       <c r="G27" t="n">
-        <v>1.440639607608318e-11</v>
+        <v>7.203198038041592e-12</v>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -2686,10 +2686,10 @@
         <v>117.4417369156242</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>57.80192017461002</v>
       </c>
       <c r="V27" t="n">
-        <v>57.80192017460281</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
         <v>146.3731429098257</v>
@@ -2975,22 +2975,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>21.29789045285992</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>129.3189095472319</v>
+        <v>0</v>
       </c>
       <c r="O31" t="n">
-        <v>171.0000000000074</v>
+        <v>150.6168000000918</v>
       </c>
       <c r="P31" t="n">
         <v>171.0000000000074</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>171.0000000000074</v>
       </c>
       <c r="R31" t="n">
         <v>171.0000000000074</v>
@@ -3093,7 +3093,7 @@
         <v>50.15547390272208</v>
       </c>
       <c r="Y32" t="n">
-        <v>-1.387372347433883e-11</v>
+        <v>-1.148596177139688e-11</v>
       </c>
     </row>
     <row r="33">
@@ -3321,16 +3321,16 @@
         <v>134.0000000000164</v>
       </c>
       <c r="V35" t="n">
-        <v>134.0000000000164</v>
+        <v>11.64150790697918</v>
       </c>
       <c r="W35" t="n">
         <v>134.0000000000164</v>
       </c>
       <c r="X35" t="n">
-        <v>0</v>
+        <v>110.2818334606671</v>
       </c>
       <c r="Y35" t="n">
-        <v>17.24077405043574</v>
+        <v>29.31743268280582</v>
       </c>
     </row>
     <row r="36">
@@ -3862,13 +3862,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
+        <v>0</v>
+      </c>
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
         <v>118.0272000002394</v>
-      </c>
-      <c r="S42" t="n">
-        <v>0</v>
-      </c>
-      <c r="T42" t="n">
-        <v>0</v>
       </c>
       <c r="U42" t="n">
         <v>0</v>
@@ -3926,19 +3926,19 @@
         <v>98.29789045285253</v>
       </c>
       <c r="M43" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P43" t="n">
+        <v>58.76445792241216</v>
+      </c>
+      <c r="Q43" t="n">
         <v>134.0000000000255</v>
-      </c>
-      <c r="N43" t="n">
-        <v>58.76445792241216</v>
-      </c>
-      <c r="O43" t="n">
-        <v>0</v>
-      </c>
-      <c r="P43" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q43" t="n">
-        <v>0</v>
       </c>
       <c r="R43" t="n">
         <v>134.0000000000255</v>
@@ -4324,16 +4324,16 @@
         <v>53.17700079634371</v>
       </c>
       <c r="K2" t="n">
-        <v>177.8897984662915</v>
+        <v>165.0600498918211</v>
       </c>
       <c r="L2" t="n">
-        <v>303.6197984662915</v>
+        <v>290.7900498918211</v>
       </c>
       <c r="M2" t="n">
-        <v>303.6197984662915</v>
+        <v>290.7900498918211</v>
       </c>
       <c r="N2" t="n">
-        <v>303.6197984662915</v>
+        <v>290.7900498918211</v>
       </c>
       <c r="O2" t="n">
         <v>382.2700000000003</v>
@@ -4555,28 +4555,28 @@
         <v>14.33796831433001</v>
       </c>
       <c r="I5" t="n">
-        <v>14.33796831433001</v>
+        <v>26.04795766400623</v>
       </c>
       <c r="J5" t="n">
-        <v>54.29676002113784</v>
+        <v>66.00674937081405</v>
       </c>
       <c r="K5" t="n">
-        <v>166.1798091166152</v>
+        <v>177.8897984662915</v>
       </c>
       <c r="L5" t="n">
-        <v>291.9098091166152</v>
+        <v>303.6197984662915</v>
       </c>
       <c r="M5" t="n">
-        <v>291.9098091166152</v>
+        <v>303.6197984662915</v>
       </c>
       <c r="N5" t="n">
-        <v>291.9098091166152</v>
+        <v>303.6197984662915</v>
       </c>
       <c r="O5" t="n">
-        <v>370.560010650324</v>
+        <v>382.2700000000003</v>
       </c>
       <c r="P5" t="n">
-        <v>496.2900106503241</v>
+        <v>508.0000000000003</v>
       </c>
       <c r="Q5" t="n">
         <v>508.0000000000003</v>
@@ -4588,7 +4588,7 @@
         <v>508.0000000000003</v>
       </c>
       <c r="T5" t="n">
-        <v>395.0084848484837</v>
+        <v>508.0000000000003</v>
       </c>
       <c r="U5" t="n">
         <v>395.0084848484837</v>
@@ -4613,22 +4613,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>278.0175922026739</v>
+        <v>281.590113364201</v>
       </c>
       <c r="C6" t="n">
-        <v>278.0175922026739</v>
+        <v>281.590113364201</v>
       </c>
       <c r="D6" t="n">
-        <v>278.0175922026739</v>
+        <v>281.590113364201</v>
       </c>
       <c r="E6" t="n">
-        <v>337.7422159529805</v>
+        <v>293.6427691981623</v>
       </c>
       <c r="F6" t="n">
-        <v>400.4723360384825</v>
+        <v>356.3728892836643</v>
       </c>
       <c r="G6" t="n">
-        <v>477.4308004278659</v>
+        <v>433.3313536730477</v>
       </c>
       <c r="H6" t="n">
         <v>508.0000000000003</v>
@@ -4682,7 +4682,7 @@
         <v>278.0175922026739</v>
       </c>
       <c r="Y6" t="n">
-        <v>278.0175922026739</v>
+        <v>281.590113364201</v>
       </c>
     </row>
     <row r="7">
@@ -4725,16 +4725,16 @@
         <v>508.0000000000003</v>
       </c>
       <c r="M7" t="n">
-        <v>452.2817470515728</v>
+        <v>508.0000000000003</v>
       </c>
       <c r="N7" t="n">
-        <v>343.9989752090033</v>
+        <v>508.0000000000003</v>
       </c>
       <c r="O7" t="n">
+        <v>395.0084848484782</v>
+      </c>
+      <c r="P7" t="n">
         <v>266.7256565656498</v>
-      </c>
-      <c r="P7" t="n">
-        <v>138.4428282828215</v>
       </c>
       <c r="Q7" t="n">
         <v>138.4428282828215</v>
@@ -4789,34 +4789,34 @@
         <v>14.04937009306006</v>
       </c>
       <c r="H8" t="n">
-        <v>14.04937009306006</v>
+        <v>20.07757918259897</v>
       </c>
       <c r="I8" t="n">
-        <v>14.04937009306006</v>
+        <v>20.07757918259897</v>
       </c>
       <c r="J8" t="n">
-        <v>54.00816179986789</v>
+        <v>60.03637088940681</v>
       </c>
       <c r="K8" t="n">
-        <v>165.8912108953453</v>
+        <v>171.9194199848842</v>
       </c>
       <c r="L8" t="n">
-        <v>304.4912108953453</v>
+        <v>310.5194199848842</v>
       </c>
       <c r="M8" t="n">
-        <v>304.4912108953453</v>
+        <v>310.5194199848843</v>
       </c>
       <c r="N8" t="n">
-        <v>304.4912108953453</v>
+        <v>310.5194199848843</v>
       </c>
       <c r="O8" t="n">
-        <v>383.1414124290541</v>
+        <v>389.1696215185931</v>
       </c>
       <c r="P8" t="n">
-        <v>509.338732486267</v>
+        <v>515.366941575806</v>
       </c>
       <c r="Q8" t="n">
-        <v>509.338732486267</v>
+        <v>515.366941575806</v>
       </c>
       <c r="R8" t="n">
         <v>560.0000000000007</v>
@@ -4825,7 +4825,7 @@
         <v>560.0000000000007</v>
       </c>
       <c r="T8" t="n">
-        <v>560.0000000000007</v>
+        <v>435.4424242424221</v>
       </c>
       <c r="U8" t="n">
         <v>435.4424242424221</v>
@@ -4856,13 +4856,13 @@
         <v>16.75252116152556</v>
       </c>
       <c r="D9" t="n">
-        <v>21.2564234888699</v>
+        <v>16.75252116152556</v>
       </c>
       <c r="E9" t="n">
-        <v>82.9610472391773</v>
+        <v>16.75252116152556</v>
       </c>
       <c r="F9" t="n">
-        <v>147.6711673246801</v>
+        <v>68.7327029352959</v>
       </c>
       <c r="G9" t="n">
         <v>147.6711673246801</v>
@@ -4929,25 +4929,25 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="C10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="D10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="E10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="F10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="G10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="H10" t="n">
-        <v>103.9049115483322</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="I10" t="n">
         <v>242.5049115483323</v>
@@ -4962,10 +4962,10 @@
         <v>560.0000000000007</v>
       </c>
       <c r="M10" t="n">
-        <v>506.301949071776</v>
+        <v>541.7049940647815</v>
       </c>
       <c r="N10" t="n">
-        <v>506.301949071776</v>
+        <v>435.4424242424149</v>
       </c>
       <c r="O10" t="n">
         <v>435.4424242424149</v>
@@ -4983,22 +4983,22 @@
         <v>60.27599984826276</v>
       </c>
       <c r="T10" t="n">
-        <v>60.27599984826276</v>
+        <v>198.8759998482628</v>
       </c>
       <c r="U10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="V10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="W10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="X10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
       <c r="Y10" t="n">
-        <v>60.27599984826276</v>
+        <v>242.5049115483323</v>
       </c>
     </row>
     <row r="11">
@@ -5029,31 +5029,31 @@
         <v>13.11999999997965</v>
       </c>
       <c r="I11" t="n">
-        <v>115.6082580058729</v>
+        <v>13.11999999997965</v>
       </c>
       <c r="J11" t="n">
-        <v>200.4686135347065</v>
+        <v>53.07879170678749</v>
       </c>
       <c r="K11" t="n">
-        <v>312.3516626301839</v>
+        <v>164.9618408022649</v>
       </c>
       <c r="L11" t="n">
-        <v>451.1524784090784</v>
+        <v>303.7626565811594</v>
       </c>
       <c r="M11" t="n">
-        <v>451.1524784090784</v>
+        <v>307.6717692892889</v>
       </c>
       <c r="N11" t="n">
-        <v>451.1524784090784</v>
+        <v>307.6717692892889</v>
       </c>
       <c r="O11" t="n">
-        <v>529.8026799427872</v>
+        <v>386.3219708229977</v>
       </c>
       <c r="P11" t="n">
-        <v>656.0000000000001</v>
+        <v>512.5192908802106</v>
       </c>
       <c r="Q11" t="n">
-        <v>656.0000000000001</v>
+        <v>512.5192908802106</v>
       </c>
       <c r="R11" t="n">
         <v>656.0000000000001</v>
@@ -5065,13 +5065,13 @@
         <v>656.0000000000001</v>
       </c>
       <c r="U11" t="n">
-        <v>510.089696969695</v>
+        <v>490.3434343434344</v>
       </c>
       <c r="V11" t="n">
-        <v>344.4331313131293</v>
+        <v>324.6868686868687</v>
       </c>
       <c r="W11" t="n">
-        <v>178.7765656565635</v>
+        <v>159.030303030303</v>
       </c>
       <c r="X11" t="n">
         <v>13.11999999999784</v>
@@ -5114,19 +5114,19 @@
         <v>219.5576647448968</v>
       </c>
       <c r="K12" t="n">
-        <v>381.9176647448968</v>
+        <v>219.5576647448968</v>
       </c>
       <c r="L12" t="n">
-        <v>381.9176647448968</v>
+        <v>219.5576647448968</v>
       </c>
       <c r="M12" t="n">
-        <v>381.9176647448968</v>
+        <v>219.5576647448968</v>
       </c>
       <c r="N12" t="n">
-        <v>493.6400000000001</v>
+        <v>331.2800000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>493.6400000000001</v>
+        <v>331.2800000000001</v>
       </c>
       <c r="P12" t="n">
         <v>493.6400000000001</v>
@@ -5166,55 +5166,55 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>315.2862409556818</v>
+        <v>269.251009962896</v>
       </c>
       <c r="C13" t="n">
-        <v>381.8882467741196</v>
+        <v>327.2160675329604</v>
       </c>
       <c r="D13" t="n">
-        <v>435.8073908991216</v>
+        <v>381.1352116579625</v>
       </c>
       <c r="E13" t="n">
-        <v>494.2362951105366</v>
+        <v>439.5641158693775</v>
       </c>
       <c r="F13" t="n">
-        <v>559.1972677024741</v>
+        <v>504.5250884613149</v>
       </c>
       <c r="G13" t="n">
-        <v>559.1972677024741</v>
+        <v>504.5250884613149</v>
       </c>
       <c r="H13" t="n">
-        <v>559.1972677024741</v>
+        <v>504.5250884613149</v>
       </c>
       <c r="I13" t="n">
-        <v>559.1972677024741</v>
+        <v>656.0000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>559.1972677024741</v>
+        <v>656.0000000000001</v>
       </c>
       <c r="K13" t="n">
         <v>656.0000000000001</v>
       </c>
       <c r="L13" t="n">
-        <v>656.0000000000001</v>
+        <v>631.4566763102434</v>
       </c>
       <c r="M13" t="n">
-        <v>656.0000000000001</v>
+        <v>525.6738211934638</v>
       </c>
       <c r="N13" t="n">
-        <v>510.089696969684</v>
+        <v>525.6738211934638</v>
       </c>
       <c r="O13" t="n">
-        <v>344.4331313131183</v>
+        <v>360.0172555368981</v>
       </c>
       <c r="P13" t="n">
-        <v>344.4331313131183</v>
+        <v>360.0172555368981</v>
       </c>
       <c r="Q13" t="n">
-        <v>178.7765656565526</v>
+        <v>194.3606898803324</v>
       </c>
       <c r="R13" t="n">
-        <v>13.11999999998693</v>
+        <v>28.7041242237667</v>
       </c>
       <c r="S13" t="n">
         <v>13.11999999998693</v>
@@ -5281,10 +5281,10 @@
         <v>377.7987917067959</v>
       </c>
       <c r="N14" t="n">
-        <v>414.9897984663058</v>
+        <v>377.7987917067959</v>
       </c>
       <c r="O14" t="n">
-        <v>493.6400000000147</v>
+        <v>529.8026799428018</v>
       </c>
       <c r="P14" t="n">
         <v>656.0000000000147</v>
@@ -5299,16 +5299,16 @@
         <v>656.0000000000147</v>
       </c>
       <c r="T14" t="n">
+        <v>656.0000000000147</v>
+      </c>
+      <c r="U14" t="n">
         <v>490.343434343449</v>
       </c>
-      <c r="U14" t="n">
+      <c r="V14" t="n">
         <v>324.6868686868833</v>
       </c>
-      <c r="V14" t="n">
+      <c r="W14" t="n">
         <v>159.0303030303176</v>
-      </c>
-      <c r="W14" t="n">
-        <v>13.11999999998807</v>
       </c>
       <c r="X14" t="n">
         <v>13.11999999998807</v>
@@ -5324,7 +5324,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14.77816231609749</v>
+        <v>19.28152772273282</v>
       </c>
       <c r="C15" t="n">
         <v>13.11999999998807</v>
@@ -5351,19 +5351,19 @@
         <v>239.2609607570024</v>
       </c>
       <c r="K15" t="n">
-        <v>401.6209607570024</v>
+        <v>331.2800000000146</v>
       </c>
       <c r="L15" t="n">
-        <v>493.6400000000147</v>
+        <v>331.2800000000146</v>
       </c>
       <c r="M15" t="n">
-        <v>493.6400000000147</v>
+        <v>331.2800000000146</v>
       </c>
       <c r="N15" t="n">
-        <v>493.6400000000147</v>
+        <v>331.2800000000146</v>
       </c>
       <c r="O15" t="n">
-        <v>493.6400000000147</v>
+        <v>331.2800000000146</v>
       </c>
       <c r="P15" t="n">
         <v>493.6400000000147</v>
@@ -5393,7 +5393,7 @@
         <v>89.47306071251869</v>
       </c>
       <c r="Y15" t="n">
-        <v>44.63327003965772</v>
+        <v>49.13663544629304</v>
       </c>
     </row>
     <row r="16">
@@ -5403,25 +5403,25 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>381.0083476291913</v>
+        <v>465.2968889504274</v>
       </c>
       <c r="C16" t="n">
-        <v>462.460353447629</v>
+        <v>546.7488947688652</v>
       </c>
       <c r="D16" t="n">
-        <v>531.2294975726311</v>
+        <v>546.7488947688652</v>
       </c>
       <c r="E16" t="n">
-        <v>604.5084017840461</v>
+        <v>546.7488947688652</v>
       </c>
       <c r="F16" t="n">
-        <v>604.5084017840461</v>
+        <v>546.7488947688652</v>
       </c>
       <c r="G16" t="n">
-        <v>604.5084017840461</v>
+        <v>656.0000000000147</v>
       </c>
       <c r="H16" t="n">
-        <v>604.5084017840461</v>
+        <v>656.0000000000147</v>
       </c>
       <c r="I16" t="n">
         <v>656.0000000000147</v>
@@ -5439,10 +5439,10 @@
         <v>656.0000000000147</v>
       </c>
       <c r="N16" t="n">
-        <v>656.0000000000147</v>
+        <v>510.0896969696852</v>
       </c>
       <c r="O16" t="n">
-        <v>510.0896969696852</v>
+        <v>344.4331313131195</v>
       </c>
       <c r="P16" t="n">
         <v>344.4331313131195</v>
@@ -5457,22 +5457,22 @@
         <v>13.11999999998807</v>
       </c>
       <c r="T16" t="n">
-        <v>13.11999999998807</v>
+        <v>49.61793945947181</v>
       </c>
       <c r="U16" t="n">
-        <v>13.11999999998807</v>
+        <v>49.61793945947181</v>
       </c>
       <c r="V16" t="n">
-        <v>13.11999999998807</v>
+        <v>203.8893323454197</v>
       </c>
       <c r="W16" t="n">
-        <v>140.4609182596674</v>
+        <v>331.2302506050991</v>
       </c>
       <c r="X16" t="n">
-        <v>246.9417092838629</v>
+        <v>331.2302506050991</v>
       </c>
       <c r="Y16" t="n">
-        <v>313.8010099628972</v>
+        <v>398.0895512841333</v>
       </c>
     </row>
     <row r="17">
@@ -5503,31 +5503,31 @@
         <v>29.91757918258976</v>
       </c>
       <c r="I17" t="n">
-        <v>65.76845680660486</v>
+        <v>29.91757918258976</v>
       </c>
       <c r="J17" t="n">
-        <v>105.7272485134127</v>
+        <v>69.87637088939761</v>
       </c>
       <c r="K17" t="n">
-        <v>217.6102976088901</v>
+        <v>181.759419984875</v>
       </c>
       <c r="L17" t="n">
-        <v>356.4111133877846</v>
+        <v>320.5602357637695</v>
       </c>
       <c r="M17" t="n">
-        <v>356.4111133877845</v>
+        <v>320.5602357637695</v>
       </c>
       <c r="N17" t="n">
-        <v>356.4111133877844</v>
+        <v>320.5602357637695</v>
       </c>
       <c r="O17" t="n">
-        <v>435.0613149214932</v>
+        <v>399.2104372974783</v>
       </c>
       <c r="P17" t="n">
-        <v>561.2586349787061</v>
+        <v>525.4077573546912</v>
       </c>
       <c r="Q17" t="n">
-        <v>561.2586349787061</v>
+        <v>525.4077573546912</v>
       </c>
       <c r="R17" t="n">
         <v>656.0000000000329</v>
@@ -5539,13 +5539,13 @@
         <v>490.3434343434662</v>
       </c>
       <c r="U17" t="n">
-        <v>490.3434343434662</v>
+        <v>324.6868686868996</v>
       </c>
       <c r="V17" t="n">
-        <v>324.6868686868996</v>
+        <v>159.030303030333</v>
       </c>
       <c r="W17" t="n">
-        <v>159.030303030333</v>
+        <v>13.11999999997352</v>
       </c>
       <c r="X17" t="n">
         <v>13.11999999997352</v>
@@ -5561,25 +5561,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>486.69272653109</v>
+        <v>483.170046077558</v>
       </c>
       <c r="C18" t="n">
-        <v>486.69272653109</v>
+        <v>483.170046077558</v>
       </c>
       <c r="D18" t="n">
-        <v>486.69272653109</v>
+        <v>541.6417360488351</v>
       </c>
       <c r="E18" t="n">
-        <v>508.391415525142</v>
+        <v>541.6417360488351</v>
       </c>
       <c r="F18" t="n">
-        <v>575.0815356106467</v>
+        <v>541.6417360488351</v>
       </c>
       <c r="G18" t="n">
-        <v>656.0000000000329</v>
+        <v>541.6417360488351</v>
       </c>
       <c r="H18" t="n">
-        <v>656.0000000000329</v>
+        <v>541.6417360488351</v>
       </c>
       <c r="I18" t="n">
         <v>656.0000000000329</v>
@@ -5615,22 +5615,22 @@
         <v>492.8744472151997</v>
       </c>
       <c r="T18" t="n">
-        <v>496.3971276687317</v>
+        <v>492.8744472151997</v>
       </c>
       <c r="U18" t="n">
-        <v>503.1498323552063</v>
+        <v>499.6271519016742</v>
       </c>
       <c r="V18" t="n">
-        <v>495.5632998385221</v>
+        <v>492.0406193849901</v>
       </c>
       <c r="W18" t="n">
-        <v>469.93386255587</v>
+        <v>466.4111821023379</v>
       </c>
       <c r="X18" t="n">
-        <v>456.9411964494208</v>
+        <v>453.4185159958887</v>
       </c>
       <c r="Y18" t="n">
-        <v>464.4737176109506</v>
+        <v>460.9510371574185</v>
       </c>
     </row>
     <row r="19">
@@ -5697,10 +5697,10 @@
         <v>64.17599984824781</v>
       </c>
       <c r="U19" t="n">
-        <v>226.5359998482487</v>
+        <v>64.17599984824781</v>
       </c>
       <c r="V19" t="n">
-        <v>226.5359998482487</v>
+        <v>64.17599984824781</v>
       </c>
       <c r="W19" t="n">
         <v>226.5359998482487</v>
@@ -5719,76 +5719,76 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13.67999999994117</v>
+        <v>13.67999999994095</v>
       </c>
       <c r="C20" t="n">
-        <v>13.67999999994117</v>
+        <v>13.67999999994095</v>
       </c>
       <c r="D20" t="n">
-        <v>13.67999999992116</v>
+        <v>13.67999999992094</v>
       </c>
       <c r="E20" t="n">
-        <v>16.29034328912289</v>
+        <v>16.29034328912266</v>
       </c>
       <c r="F20" t="n">
-        <v>18.37961086819284</v>
+        <v>18.37961086819261</v>
       </c>
       <c r="G20" t="n">
-        <v>22.46937009299321</v>
+        <v>22.46937009299298</v>
       </c>
       <c r="H20" t="n">
-        <v>30.47757918253291</v>
+        <v>30.47757918253268</v>
       </c>
       <c r="I20" t="n">
-        <v>86.62578343977108</v>
+        <v>56.38556490047264</v>
       </c>
       <c r="J20" t="n">
-        <v>126.5845751465789</v>
+        <v>96.34435660728047</v>
       </c>
       <c r="K20" t="n">
-        <v>238.4676242420563</v>
+        <v>208.2274057027579</v>
       </c>
       <c r="L20" t="n">
-        <v>377.2684400209508</v>
+        <v>347.0282214816524</v>
       </c>
       <c r="M20" t="n">
-        <v>479.1524784091196</v>
+        <v>347.0282214816523</v>
       </c>
       <c r="N20" t="n">
-        <v>479.1524784091196</v>
+        <v>347.0282214816523</v>
       </c>
       <c r="O20" t="n">
-        <v>557.8026799428284</v>
+        <v>425.6784230153611</v>
       </c>
       <c r="P20" t="n">
-        <v>684.0000000000413</v>
+        <v>551.875743072574</v>
       </c>
       <c r="Q20" t="n">
-        <v>684.0000000000413</v>
+        <v>551.875743072574</v>
       </c>
       <c r="R20" t="n">
-        <v>684.0000000000413</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="S20" t="n">
-        <v>684.0000000000413</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="T20" t="n">
-        <v>511.2727272727656</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="U20" t="n">
-        <v>511.2727272727656</v>
+        <v>511.2727272727657</v>
       </c>
       <c r="V20" t="n">
-        <v>338.5454545454899</v>
+        <v>338.54545454549</v>
       </c>
       <c r="W20" t="n">
         <v>165.8181818182142</v>
       </c>
       <c r="X20" t="n">
-        <v>13.67999999994117</v>
+        <v>13.67999999994095</v>
       </c>
       <c r="Y20" t="n">
-        <v>13.67999999995436</v>
+        <v>13.67999999995413</v>
       </c>
     </row>
     <row r="21">
@@ -5798,76 +5798,76 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>21.21252116146986</v>
+        <v>21.21252116146963</v>
       </c>
       <c r="C21" t="n">
-        <v>21.21252116146986</v>
+        <v>21.21252116146963</v>
       </c>
       <c r="D21" t="n">
-        <v>21.21252116146986</v>
+        <v>21.21252116146963</v>
       </c>
       <c r="E21" t="n">
-        <v>21.21252116146986</v>
+        <v>21.21252116146963</v>
       </c>
       <c r="F21" t="n">
-        <v>53.19169283422214</v>
+        <v>53.19169283422191</v>
       </c>
       <c r="G21" t="n">
-        <v>134.1101572236071</v>
+        <v>134.1101572236069</v>
       </c>
       <c r="H21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="I21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="J21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="K21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="L21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="M21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="N21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="O21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="P21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="Q21" t="n">
-        <v>212.7388035505613</v>
+        <v>212.7388035505611</v>
       </c>
       <c r="R21" t="n">
-        <v>100.8601441929091</v>
+        <v>100.8601441929089</v>
       </c>
       <c r="S21" t="n">
-        <v>49.61325076572581</v>
+        <v>49.61325076572558</v>
       </c>
       <c r="T21" t="n">
-        <v>53.13593121925675</v>
+        <v>53.13593121925652</v>
       </c>
       <c r="U21" t="n">
-        <v>59.88863590573016</v>
+        <v>59.88863590572993</v>
       </c>
       <c r="V21" t="n">
-        <v>52.30210338904486</v>
+        <v>52.30210338904463</v>
       </c>
       <c r="W21" t="n">
-        <v>26.67266610639152</v>
+        <v>26.67266610639129</v>
       </c>
       <c r="X21" t="n">
-        <v>13.67999999994117</v>
+        <v>13.67999999994095</v>
       </c>
       <c r="Y21" t="n">
-        <v>21.21252116146986</v>
+        <v>21.21252116146963</v>
       </c>
     </row>
     <row r="22">
@@ -5877,37 +5877,37 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>132.3673376662482</v>
+        <v>419.9966383452517</v>
       </c>
       <c r="C22" t="n">
-        <v>265.2993434846857</v>
+        <v>419.9966383452517</v>
       </c>
       <c r="D22" t="n">
-        <v>385.5484876096874</v>
+        <v>540.2457824702534</v>
       </c>
       <c r="E22" t="n">
-        <v>385.5484876096874</v>
+        <v>540.2457824702534</v>
       </c>
       <c r="F22" t="n">
-        <v>385.5484876096874</v>
+        <v>540.2457824702534</v>
       </c>
       <c r="G22" t="n">
-        <v>385.5484876096874</v>
+        <v>540.2457824702534</v>
       </c>
       <c r="H22" t="n">
-        <v>385.5484876096874</v>
+        <v>540.2457824702534</v>
       </c>
       <c r="I22" t="n">
-        <v>554.8384876096903</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="J22" t="n">
-        <v>641.7249115483721</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="K22" t="n">
-        <v>641.7249115483721</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="L22" t="n">
-        <v>684.0000000000413</v>
+        <v>684.0000000000415</v>
       </c>
       <c r="M22" t="n">
         <v>636.1041859839121</v>
@@ -5916,37 +5916,37 @@
         <v>531.8618181817483</v>
       </c>
       <c r="O22" t="n">
-        <v>531.8618181817483</v>
+        <v>359.1345454544725</v>
       </c>
       <c r="P22" t="n">
-        <v>359.1345454544726</v>
+        <v>186.4072727271967</v>
       </c>
       <c r="Q22" t="n">
-        <v>186.4072727271969</v>
+        <v>13.67999999992094</v>
       </c>
       <c r="R22" t="n">
-        <v>13.67999999992116</v>
+        <v>13.67999999992094</v>
       </c>
       <c r="S22" t="n">
-        <v>13.67999999992116</v>
+        <v>13.67999999992094</v>
       </c>
       <c r="T22" t="n">
-        <v>13.67999999992116</v>
+        <v>182.9699999999239</v>
       </c>
       <c r="U22" t="n">
-        <v>13.67999999992116</v>
+        <v>182.9699999999239</v>
       </c>
       <c r="V22" t="n">
-        <v>13.67999999992116</v>
+        <v>182.9699999999239</v>
       </c>
       <c r="W22" t="n">
-        <v>13.67999999995436</v>
+        <v>182.9699999999239</v>
       </c>
       <c r="X22" t="n">
-        <v>13.67999999995436</v>
+        <v>182.9699999999239</v>
       </c>
       <c r="Y22" t="n">
-        <v>13.67999999995436</v>
+        <v>301.3093006789578</v>
       </c>
     </row>
     <row r="23">
@@ -5977,22 +5977,22 @@
         <v>32.71757918250914</v>
       </c>
       <c r="I23" t="n">
-        <v>199.5558371884014</v>
+        <v>318.9963827549439</v>
       </c>
       <c r="J23" t="n">
-        <v>239.5146288952093</v>
+        <v>418.6405210630047</v>
       </c>
       <c r="K23" t="n">
-        <v>411.0830245919392</v>
+        <v>530.523570158482</v>
       </c>
       <c r="L23" t="n">
-        <v>549.8838403708337</v>
+        <v>669.3243859373766</v>
       </c>
       <c r="M23" t="n">
-        <v>562.95197082304</v>
+        <v>779.3217692893351</v>
       </c>
       <c r="N23" t="n">
-        <v>562.95197082304</v>
+        <v>779.3217692893351</v>
       </c>
       <c r="O23" t="n">
         <v>857.9719708230439</v>
@@ -6035,76 +6035,76 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>978.1173223699352</v>
+        <v>23.83999999994967</v>
       </c>
       <c r="C24" t="n">
-        <v>978.1173223699352</v>
+        <v>42.11485360304829</v>
       </c>
       <c r="D24" t="n">
-        <v>978.1173223699352</v>
+        <v>98.60654357432369</v>
       </c>
       <c r="E24" t="n">
-        <v>978.1173223699352</v>
+        <v>160.3111673246312</v>
       </c>
       <c r="F24" t="n">
-        <v>978.1173223699352</v>
+        <v>160.3111673246312</v>
       </c>
       <c r="G24" t="n">
-        <v>978.1173223699352</v>
+        <v>160.3111673246312</v>
       </c>
       <c r="H24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="I24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="J24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="K24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="L24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="M24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="N24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="O24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="P24" t="n">
-        <v>978.1173223699352</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="Q24" t="n">
-        <v>1192.000000000045</v>
+        <v>236.9598136515847</v>
       </c>
       <c r="R24" t="n">
-        <v>1078.10113862219</v>
+        <v>123.0609522737298</v>
       </c>
       <c r="S24" t="n">
-        <v>1024.834043174804</v>
+        <v>69.79385682634378</v>
       </c>
       <c r="T24" t="n">
-        <v>1024.834043174804</v>
+        <v>71.33653727987405</v>
       </c>
       <c r="U24" t="n">
-        <v>1024.834043174804</v>
+        <v>76.10924196634679</v>
       </c>
       <c r="V24" t="n">
-        <v>1015.227308637916</v>
+        <v>66.50250742945877</v>
       </c>
       <c r="W24" t="n">
-        <v>987.5776693350602</v>
+        <v>38.85286812660272</v>
       </c>
       <c r="X24" t="n">
-        <v>972.5648012084072</v>
+        <v>23.83999999994967</v>
       </c>
       <c r="Y24" t="n">
-        <v>978.1173223699352</v>
+        <v>23.83999999994967</v>
       </c>
     </row>
     <row r="25">
@@ -6114,31 +6114,31 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>433.747556604905</v>
+        <v>742.9720625339141</v>
       </c>
       <c r="C25" t="n">
-        <v>564.6995624233417</v>
+        <v>742.9720625339141</v>
       </c>
       <c r="D25" t="n">
-        <v>682.9687065483428</v>
+        <v>861.2412066589152</v>
       </c>
       <c r="E25" t="n">
-        <v>805.7476107597568</v>
+        <v>861.2412066589152</v>
       </c>
       <c r="F25" t="n">
-        <v>935.0585833516932</v>
+        <v>990.5521792508516</v>
       </c>
       <c r="G25" t="n">
-        <v>935.0585833516932</v>
+        <v>990.5521792508516</v>
       </c>
       <c r="H25" t="n">
-        <v>1113.032981953715</v>
+        <v>990.5521792508516</v>
       </c>
       <c r="I25" t="n">
-        <v>1113.032981953715</v>
+        <v>990.5521792508516</v>
       </c>
       <c r="J25" t="n">
-        <v>1113.032981953715</v>
+        <v>990.5521792508516</v>
       </c>
       <c r="K25" t="n">
         <v>1151.704911548377</v>
@@ -6171,19 +6171,19 @@
         <v>23.8399999999001</v>
       </c>
       <c r="U25" t="n">
-        <v>23.8399999999001</v>
+        <v>275.3627129660566</v>
       </c>
       <c r="V25" t="n">
-        <v>23.8399999999001</v>
+        <v>479.1341058520036</v>
       </c>
       <c r="W25" t="n">
-        <v>200.6809182595785</v>
+        <v>479.1341058520036</v>
       </c>
       <c r="X25" t="n">
-        <v>200.6809182595785</v>
+        <v>635.1148968761981</v>
       </c>
       <c r="Y25" t="n">
-        <v>317.0402189386118</v>
+        <v>635.1148968761981</v>
       </c>
     </row>
     <row r="26">
@@ -6214,31 +6214,31 @@
         <v>13.67999999992958</v>
       </c>
       <c r="I26" t="n">
-        <v>13.67999999992958</v>
+        <v>62.70825800582366</v>
       </c>
       <c r="J26" t="n">
-        <v>53.63879170673741</v>
+        <v>102.6670497126315</v>
       </c>
       <c r="K26" t="n">
-        <v>222.9287917067374</v>
+        <v>214.5500988081089</v>
       </c>
       <c r="L26" t="n">
-        <v>361.729607485632</v>
+        <v>353.3509145870034</v>
       </c>
       <c r="M26" t="n">
-        <v>361.729607485632</v>
+        <v>479.1524784091016</v>
       </c>
       <c r="N26" t="n">
-        <v>389.1317692893113</v>
+        <v>479.1524784091016</v>
       </c>
       <c r="O26" t="n">
-        <v>467.7819708230201</v>
+        <v>557.8026799428104</v>
       </c>
       <c r="P26" t="n">
-        <v>593.979290880233</v>
+        <v>684.0000000000233</v>
       </c>
       <c r="Q26" t="n">
-        <v>593.979290880233</v>
+        <v>684.0000000000233</v>
       </c>
       <c r="R26" t="n">
         <v>684.0000000000233</v>
@@ -6250,13 +6250,13 @@
         <v>684.0000000000233</v>
       </c>
       <c r="U26" t="n">
-        <v>531.8618181817939</v>
+        <v>511.2727272727449</v>
       </c>
       <c r="V26" t="n">
-        <v>359.1345454545155</v>
+        <v>338.5454545454664</v>
       </c>
       <c r="W26" t="n">
-        <v>186.4072727272371</v>
+        <v>165.818181818188</v>
       </c>
       <c r="X26" t="n">
         <v>13.67999999995868</v>
@@ -6275,16 +6275,16 @@
         <v>13.67999999995868</v>
       </c>
       <c r="C27" t="n">
-        <v>13.67999999995868</v>
+        <v>13.67999999995141</v>
       </c>
       <c r="D27" t="n">
-        <v>13.67999999995868</v>
+        <v>13.67999999995141</v>
       </c>
       <c r="E27" t="n">
-        <v>13.67999999995868</v>
+        <v>13.67999999995141</v>
       </c>
       <c r="F27" t="n">
-        <v>13.67999999995868</v>
+        <v>13.67999999995141</v>
       </c>
       <c r="G27" t="n">
         <v>13.67999999994413</v>
@@ -6299,19 +6299,19 @@
         <v>249.8074162335363</v>
       </c>
       <c r="K27" t="n">
-        <v>249.8074162335363</v>
+        <v>280.2030576613014</v>
       </c>
       <c r="L27" t="n">
-        <v>249.8074162335363</v>
+        <v>280.2030576613014</v>
       </c>
       <c r="M27" t="n">
-        <v>249.8074162335363</v>
+        <v>301.6862771783572</v>
       </c>
       <c r="N27" t="n">
-        <v>249.8074162335363</v>
+        <v>359.9486124334613</v>
       </c>
       <c r="O27" t="n">
-        <v>359.9486124334613</v>
+        <v>529.2386124334669</v>
       </c>
       <c r="P27" t="n">
         <v>529.2386124334669</v>
@@ -6329,13 +6329,13 @@
         <v>219.9174374589774</v>
       </c>
       <c r="U27" t="n">
-        <v>219.9174374589774</v>
+        <v>161.5316595048258</v>
       </c>
       <c r="V27" t="n">
-        <v>161.5316595048331</v>
+        <v>161.5316595048258</v>
       </c>
       <c r="W27" t="n">
-        <v>13.67999999995868</v>
+        <v>13.67999999995141</v>
       </c>
       <c r="X27" t="n">
         <v>13.67999999995868</v>
@@ -6351,28 +6351,28 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>404.8520480722043</v>
+        <v>281.3484722467163</v>
       </c>
       <c r="C28" t="n">
-        <v>417.9940538906429</v>
+        <v>281.3484722467163</v>
       </c>
       <c r="D28" t="n">
-        <v>418.4531980156457</v>
+        <v>281.8076163717191</v>
       </c>
       <c r="E28" t="n">
-        <v>423.4221022270616</v>
+        <v>286.776520583135</v>
       </c>
       <c r="F28" t="n">
-        <v>434.9230748189999</v>
+        <v>298.2774931750733</v>
       </c>
       <c r="G28" t="n">
-        <v>475.8641800501503</v>
+        <v>339.2185984062237</v>
       </c>
       <c r="H28" t="n">
-        <v>536.0285786521737</v>
+        <v>399.382997008247</v>
       </c>
       <c r="I28" t="n">
-        <v>634.0434901908598</v>
+        <v>497.3979085469331</v>
       </c>
       <c r="J28" t="n">
         <v>640.6572677024964</v>
@@ -6408,19 +6408,19 @@
         <v>90.58143817514525</v>
       </c>
       <c r="U28" t="n">
-        <v>224.2941511413036</v>
+        <v>100.7905753158155</v>
       </c>
       <c r="V28" t="n">
-        <v>310.2555440272523</v>
+        <v>186.7519682017642</v>
       </c>
       <c r="W28" t="n">
-        <v>369.2864622869325</v>
+        <v>245.7828864614445</v>
       </c>
       <c r="X28" t="n">
-        <v>407.4572533111289</v>
+        <v>283.9536774856408</v>
       </c>
       <c r="Y28" t="n">
-        <v>405.9770989177354</v>
+        <v>282.4735230922474</v>
       </c>
     </row>
     <row r="29">
@@ -6457,25 +6457,25 @@
         <v>53.63879170670854</v>
       </c>
       <c r="K29" t="n">
-        <v>222.9287917067085</v>
+        <v>165.5218408021859</v>
       </c>
       <c r="L29" t="n">
-        <v>361.729607485603</v>
+        <v>304.3226565810804</v>
       </c>
       <c r="M29" t="n">
-        <v>361.729607485603</v>
+        <v>332.7017692893199</v>
       </c>
       <c r="N29" t="n">
-        <v>425.3574933457797</v>
+        <v>332.7017692893199</v>
       </c>
       <c r="O29" t="n">
-        <v>504.0076948794886</v>
+        <v>411.3519708230288</v>
       </c>
       <c r="P29" t="n">
-        <v>630.2050149367014</v>
+        <v>537.5492908802416</v>
       </c>
       <c r="Q29" t="n">
-        <v>684.0000000000304</v>
+        <v>537.5492908802416</v>
       </c>
       <c r="R29" t="n">
         <v>684.0000000000304</v>
@@ -6539,19 +6539,19 @@
         <v>342.7192707856565</v>
       </c>
       <c r="L30" t="n">
-        <v>342.7192707856565</v>
+        <v>345.4200000000157</v>
       </c>
       <c r="M30" t="n">
-        <v>342.7192707856565</v>
+        <v>345.4200000000157</v>
       </c>
       <c r="N30" t="n">
         <v>345.4200000000157</v>
       </c>
       <c r="O30" t="n">
-        <v>345.4200000000157</v>
+        <v>514.710000000023</v>
       </c>
       <c r="P30" t="n">
-        <v>514.710000000023</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="Q30" t="n">
         <v>684.0000000000304</v>
@@ -6588,49 +6588,49 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>278.721009962822</v>
+        <v>421.460439836029</v>
       </c>
       <c r="C31" t="n">
-        <v>278.721009962822</v>
+        <v>421.460439836029</v>
       </c>
       <c r="D31" t="n">
-        <v>335.6101540878233</v>
+        <v>478.3495839610303</v>
       </c>
       <c r="E31" t="n">
-        <v>335.6101540878233</v>
+        <v>518.697922176945</v>
       </c>
       <c r="F31" t="n">
-        <v>403.5411266797599</v>
+        <v>586.6288947688817</v>
       </c>
       <c r="G31" t="n">
-        <v>467.6328691004833</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="H31" t="n">
-        <v>584.2272677025051</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="I31" t="n">
-        <v>584.2272677025051</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="J31" t="n">
-        <v>584.2272677025051</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="K31" t="n">
         <v>684.0000000000304</v>
       </c>
       <c r="L31" t="n">
-        <v>662.4869793405759</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="M31" t="n">
-        <v>662.4869793405759</v>
+        <v>684.0000000000304</v>
       </c>
       <c r="N31" t="n">
+        <v>684.0000000000304</v>
+      </c>
+      <c r="O31" t="n">
         <v>531.8618181817558</v>
       </c>
-      <c r="O31" t="n">
+      <c r="P31" t="n">
         <v>359.1345454544756</v>
-      </c>
-      <c r="P31" t="n">
-        <v>186.4072727271954</v>
       </c>
       <c r="Q31" t="n">
         <v>186.4072727271954</v>
@@ -6648,16 +6648,16 @@
         <v>13.67999999991525</v>
       </c>
       <c r="V31" t="n">
-        <v>13.67999999991525</v>
+        <v>156.0713928858624</v>
       </c>
       <c r="W31" t="n">
-        <v>129.1409182595938</v>
+        <v>271.532311145541</v>
       </c>
       <c r="X31" t="n">
-        <v>223.7417092837885</v>
+        <v>366.1331021697357</v>
       </c>
       <c r="Y31" t="n">
-        <v>278.721009962822</v>
+        <v>366.1331021697357</v>
       </c>
     </row>
     <row r="32">
@@ -6676,40 +6676,40 @@
         <v>44.84084771334415</v>
       </c>
       <c r="E32" t="n">
-        <v>121.7011910025443</v>
+        <v>44.84084771334415</v>
       </c>
       <c r="F32" t="n">
-        <v>121.7011910025443</v>
+        <v>44.84084771334415</v>
       </c>
       <c r="G32" t="n">
-        <v>121.7011910025443</v>
+        <v>44.84084771334415</v>
       </c>
       <c r="H32" t="n">
-        <v>121.7011910025443</v>
+        <v>44.84084771334415</v>
       </c>
       <c r="I32" t="n">
-        <v>121.7011910025443</v>
+        <v>44.84084771334415</v>
       </c>
       <c r="J32" t="n">
-        <v>161.6599827093521</v>
+        <v>84.79963942015198</v>
       </c>
       <c r="K32" t="n">
-        <v>273.5430318048296</v>
+        <v>196.6826885156294</v>
       </c>
       <c r="L32" t="n">
-        <v>412.3438475837241</v>
+        <v>335.4835042945239</v>
       </c>
       <c r="M32" t="n">
-        <v>412.3438475837241</v>
+        <v>335.4835042945239</v>
       </c>
       <c r="N32" t="n">
-        <v>412.3438475837241</v>
+        <v>335.4835042945239</v>
       </c>
       <c r="O32" t="n">
-        <v>490.994049117433</v>
+        <v>414.1337058282327</v>
       </c>
       <c r="P32" t="n">
-        <v>617.1913691746458</v>
+        <v>540.3310258854456</v>
       </c>
       <c r="Q32" t="n">
         <v>624.6767630087945</v>
@@ -6746,13 +6746,13 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="C33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="D33" t="n">
-        <v>632.0000000000729</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="E33" t="n">
         <v>632.0000000000729</v>
@@ -6797,25 +6797,25 @@
         <v>595.8789163999949</v>
       </c>
       <c r="S33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="T33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="U33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="V33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="W33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="X33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
       <c r="Y33" t="n">
-        <v>619.9018361520109</v>
+        <v>595.8789163999949</v>
       </c>
     </row>
     <row r="34">
@@ -6907,49 +6907,49 @@
         <v>10.72068017390657</v>
       </c>
       <c r="C35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="D35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="E35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="F35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="G35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="H35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="I35" t="n">
-        <v>10.72068017390657</v>
+        <v>39.32740061559439</v>
       </c>
       <c r="J35" t="n">
-        <v>50.6794718807144</v>
+        <v>79.28619232240221</v>
       </c>
       <c r="K35" t="n">
-        <v>162.5625209761918</v>
+        <v>191.1692414178796</v>
       </c>
       <c r="L35" t="n">
-        <v>295.2225209761918</v>
+        <v>323.8292414178796</v>
       </c>
       <c r="M35" t="n">
-        <v>295.2225209761918</v>
+        <v>323.8292414178796</v>
       </c>
       <c r="N35" t="n">
-        <v>295.2225209761918</v>
+        <v>323.8292414178796</v>
       </c>
       <c r="O35" t="n">
-        <v>373.8727225099007</v>
+        <v>402.4794429515885</v>
       </c>
       <c r="P35" t="n">
-        <v>500.0700425671135</v>
+        <v>528.6767630088013</v>
       </c>
       <c r="Q35" t="n">
-        <v>500.0700425671135</v>
+        <v>528.6767630088013</v>
       </c>
       <c r="R35" t="n">
         <v>528.6767630088013</v>
@@ -6964,13 +6964,13 @@
         <v>298.8419939902971</v>
       </c>
       <c r="V35" t="n">
-        <v>163.4884586367451</v>
+        <v>287.0828950943585</v>
       </c>
       <c r="W35" t="n">
-        <v>28.13492328319319</v>
+        <v>151.7293597408066</v>
       </c>
       <c r="X35" t="n">
-        <v>28.13492328319319</v>
+        <v>40.33356836639529</v>
       </c>
       <c r="Y35" t="n">
         <v>10.71999999992477</v>
@@ -6983,76 +6983,76 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="C36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="D36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="E36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="F36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="G36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="H36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="I36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="J36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="K36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="L36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="M36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="N36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="O36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="P36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="Q36" t="n">
-        <v>536.0000000000801</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="R36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999983746</v>
       </c>
       <c r="S36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999983746</v>
       </c>
       <c r="T36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999983746</v>
       </c>
       <c r="U36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999983746</v>
       </c>
       <c r="V36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999983746</v>
       </c>
       <c r="W36" t="n">
-        <v>499.8789164000025</v>
+        <v>10.71999999986656</v>
       </c>
       <c r="X36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
       <c r="Y36" t="n">
-        <v>499.8789164000025</v>
+        <v>46.84108359991506</v>
       </c>
     </row>
     <row r="37">
@@ -7062,19 +7062,19 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>512.3994597148335</v>
+        <v>401.345999848142</v>
       </c>
       <c r="C37" t="n">
-        <v>512.3994597148335</v>
+        <v>401.345999848142</v>
       </c>
       <c r="D37" t="n">
-        <v>512.3994597148335</v>
+        <v>401.345999848142</v>
       </c>
       <c r="E37" t="n">
-        <v>512.3994597148335</v>
+        <v>401.345999848142</v>
       </c>
       <c r="F37" t="n">
-        <v>512.3994597148335</v>
+        <v>401.345999848142</v>
       </c>
       <c r="G37" t="n">
         <v>512.3994597148335</v>
@@ -7220,76 +7220,76 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="C39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="D39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="E39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="F39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="G39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="H39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="I39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="J39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="K39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="L39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="M39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="N39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="O39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="P39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="Q39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
       <c r="R39" t="n">
-        <v>499.8789164000403</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="S39" t="n">
-        <v>499.8789164000403</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="T39" t="n">
-        <v>499.8789164000403</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="U39" t="n">
-        <v>499.8789164000403</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="V39" t="n">
-        <v>499.8789164000403</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="W39" t="n">
-        <v>536.0000000001165</v>
+        <v>10.71999999986292</v>
       </c>
       <c r="X39" t="n">
-        <v>536.0000000001165</v>
+        <v>10.71999999989202</v>
       </c>
       <c r="Y39" t="n">
-        <v>536.0000000001165</v>
+        <v>46.84108359993909</v>
       </c>
     </row>
     <row r="40">
@@ -7305,28 +7305,28 @@
         <v>268.6859998481991</v>
       </c>
       <c r="D40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="E40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="F40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="G40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="H40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="I40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="J40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="K40" t="n">
-        <v>401.3459998482207</v>
+        <v>401.3459998482657</v>
       </c>
       <c r="L40" t="n">
         <v>512.3994597148684</v>
@@ -7484,31 +7484,31 @@
         <v>57.75741623340408</v>
       </c>
       <c r="K42" t="n">
-        <v>136.3367804830228</v>
+        <v>190.4174162334293</v>
       </c>
       <c r="L42" t="n">
-        <v>268.996780483048</v>
+        <v>323.0774162334545</v>
       </c>
       <c r="M42" t="n">
-        <v>270.6800000001098</v>
+        <v>324.7606357505163</v>
       </c>
       <c r="N42" t="n">
-        <v>403.340000000135</v>
+        <v>389.3432731358929</v>
       </c>
       <c r="O42" t="n">
-        <v>536.0000000001602</v>
+        <v>389.3432731358929</v>
       </c>
       <c r="P42" t="n">
-        <v>536.0000000001602</v>
+        <v>522.0032731359181</v>
       </c>
       <c r="Q42" t="n">
         <v>536.0000000001602</v>
       </c>
       <c r="R42" t="n">
-        <v>416.7806060605244</v>
+        <v>536.0000000001602</v>
       </c>
       <c r="S42" t="n">
-        <v>416.7806060605244</v>
+        <v>536.0000000001602</v>
       </c>
       <c r="T42" t="n">
         <v>416.7806060605244</v>
@@ -7569,16 +7569,16 @@
         <v>436.7092015629354</v>
       </c>
       <c r="M43" t="n">
-        <v>301.3556662093742</v>
+        <v>436.7092015629354</v>
       </c>
       <c r="N43" t="n">
-        <v>241.9976279039074</v>
+        <v>436.7092015629354</v>
       </c>
       <c r="O43" t="n">
-        <v>241.9976279039074</v>
+        <v>436.7092015629354</v>
       </c>
       <c r="P43" t="n">
-        <v>241.9976279039074</v>
+        <v>377.3511632574686</v>
       </c>
       <c r="Q43" t="n">
         <v>241.9976279039074</v>
@@ -7718,22 +7718,22 @@
         <v>10.15999999979977</v>
       </c>
       <c r="J45" t="n">
-        <v>10.15999999979977</v>
+        <v>135.8899999998579</v>
       </c>
       <c r="K45" t="n">
-        <v>135.8899999998579</v>
+        <v>261.619999999916</v>
       </c>
       <c r="L45" t="n">
-        <v>212.7065425894439</v>
+        <v>261.619999999916</v>
       </c>
       <c r="M45" t="n">
-        <v>212.7065425894439</v>
+        <v>261.619999999916</v>
       </c>
       <c r="N45" t="n">
-        <v>338.436542589502</v>
+        <v>261.619999999916</v>
       </c>
       <c r="O45" t="n">
-        <v>444.3186124337175</v>
+        <v>318.5886124336594</v>
       </c>
       <c r="P45" t="n">
         <v>444.3186124337175</v>
@@ -7961,7 +7961,7 @@
         <v>0</v>
       </c>
       <c r="I2" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -7985,10 +7985,10 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>9.495432217177264</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>87.61110712245301</v>
+        <v>217.7535550634105</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>388.2594492503575</v>
       </c>
       <c r="N5" t="n">
-        <v>318.7219932457146</v>
+        <v>47.32911253548826</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -8222,10 +8222,10 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>88.70919257876994</v>
+        <v>76.88092050838992</v>
       </c>
       <c r="R5" t="n">
-        <v>142.1860283846698</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -8280,7 +8280,7 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>57.34518285992402</v>
       </c>
       <c r="K6" t="n">
         <v>28.01641452410897</v>
@@ -8289,7 +8289,7 @@
         <v>10.78470639412994</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>264.2997782656032</v>
       </c>
       <c r="N6" t="n">
         <v>227.1491563079784</v>
@@ -8359,7 +8359,7 @@
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>134.2003162992274</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -8435,7 +8435,7 @@
         <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>120.6470157237802</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -8450,7 +8450,7 @@
         <v>388.2594492503575</v>
       </c>
       <c r="N8" t="n">
-        <v>83.15331754459014</v>
+        <v>318.7219932457146</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -8462,7 +8462,7 @@
         <v>76.88092050838992</v>
       </c>
       <c r="R8" t="n">
-        <v>294.54111633436</v>
+        <v>149.0737810647954</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -8517,7 +8517,7 @@
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>57.34518285992402</v>
       </c>
       <c r="K9" t="n">
         <v>28.01641452410897</v>
@@ -8672,7 +8672,7 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -8684,10 +8684,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>388.2594492503575</v>
+        <v>83.25701017486173</v>
       </c>
       <c r="N11" t="n">
-        <v>286.3833075632474</v>
+        <v>318.7219932457146</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -8699,7 +8699,7 @@
         <v>76.88092050838992</v>
       </c>
       <c r="R11" t="n">
-        <v>149.6111071224515</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -8757,7 +8757,7 @@
         <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>28.01641452410897</v>
       </c>
       <c r="L12" t="n">
         <v>10.78470639412994</v>
@@ -8772,7 +8772,7 @@
         <v>28.12489953966674</v>
       </c>
       <c r="P12" t="n">
-        <v>14.7120846843868</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
         <v>0</v>
@@ -8909,7 +8909,7 @@
         <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -8921,10 +8921,10 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>292.2876413750112</v>
+        <v>388.2594492503575</v>
       </c>
       <c r="N14" t="n">
-        <v>356.2886667401691</v>
+        <v>133.9252256647727</v>
       </c>
       <c r="O14" t="n">
         <v>0</v>
@@ -8997,7 +8997,7 @@
         <v>0</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>10.78470639412994</v>
       </c>
       <c r="M15" t="n">
         <v>264.2997782656032</v>
@@ -9146,7 +9146,7 @@
         <v>0</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -9158,7 +9158,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>388.2594492503575</v>
+        <v>151.3807728210575</v>
       </c>
       <c r="N17" t="n">
         <v>318.7219932457146</v>
@@ -9173,7 +9173,7 @@
         <v>76.88092050838992</v>
       </c>
       <c r="R17" t="n">
-        <v>178.3094556288412</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -9395,7 +9395,7 @@
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>491.1726193394168</v>
+        <v>388.2594492503575</v>
       </c>
       <c r="N20" t="n">
         <v>318.7219932457146</v>
@@ -9410,7 +9410,7 @@
         <v>76.88092050838992</v>
       </c>
       <c r="R20" t="n">
-        <v>82.61110712245176</v>
+        <v>216.0699525037321</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -9465,7 +9465,7 @@
         <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>57.34518285992402</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
         <v>28.01641452410897</v>
@@ -9620,7 +9620,7 @@
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -9632,13 +9632,13 @@
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>401.4595810202628</v>
+        <v>499.3679172826389</v>
       </c>
       <c r="N23" t="n">
         <v>318.7219932457146</v>
       </c>
       <c r="O23" t="n">
-        <v>218.5553519861566</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
         <v>0</v>
@@ -9869,10 +9869,10 @@
         <v>0</v>
       </c>
       <c r="M26" t="n">
-        <v>102.2594492503546</v>
+        <v>355.9017270504875</v>
       </c>
       <c r="N26" t="n">
-        <v>184.908767618532</v>
+        <v>32.72199324571176</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -9884,7 +9884,7 @@
         <v>76.88092050838992</v>
       </c>
       <c r="R26" t="n">
-        <v>294.54111633436</v>
+        <v>203.6111071224506</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -9942,22 +9942,22 @@
         <v>0</v>
       </c>
       <c r="K27" t="n">
-        <v>28.01641452410897</v>
+        <v>58.71908263296266</v>
       </c>
       <c r="L27" t="n">
         <v>10.78470639412994</v>
       </c>
       <c r="M27" t="n">
-        <v>264.2997782656032</v>
+        <v>0</v>
       </c>
       <c r="N27" t="n">
         <v>0</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>199.1248995396724</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>14.7120846843868</v>
       </c>
       <c r="Q27" t="n">
         <v>0</v>
@@ -10094,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -10106,10 +10106,10 @@
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>388.2594492503575</v>
+        <v>120.6000873662292</v>
       </c>
       <c r="N29" t="n">
-        <v>382.9925850236709</v>
+        <v>318.7219932457146</v>
       </c>
       <c r="O29" t="n">
         <v>0</v>
@@ -10118,10 +10118,10 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>76.88092050838992</v>
       </c>
       <c r="R29" t="n">
-        <v>146.6111071224523</v>
+        <v>294.54111633436</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -10182,7 +10182,7 @@
         <v>28.01641452410897</v>
       </c>
       <c r="L30" t="n">
-        <v>10.78470639412994</v>
+        <v>13.51271570156345</v>
       </c>
       <c r="M30" t="n">
         <v>264.2997782656032</v>
@@ -10191,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>28.12489953966674</v>
+        <v>0</v>
       </c>
       <c r="P30" t="n">
         <v>0</v>
@@ -10346,7 +10346,7 @@
         <v>388.2594492503575</v>
       </c>
       <c r="N32" t="n">
-        <v>154.6731058571567</v>
+        <v>77.03639546402526</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -10355,7 +10355,7 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>84.44192438126737</v>
+        <v>162.0786347743989</v>
       </c>
       <c r="R32" t="n">
         <v>294.54111633436</v>
@@ -10580,7 +10580,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>194.3939496767518</v>
+        <v>213.8286730999704</v>
       </c>
       <c r="N35" t="n">
         <v>318.7219932457146</v>
@@ -10653,7 +10653,7 @@
         <v>57.34518285992402</v>
       </c>
       <c r="K36" t="n">
-        <v>64.5023575544904</v>
+        <v>28.01641452410897</v>
       </c>
       <c r="L36" t="n">
         <v>10.78470639412994</v>
@@ -10805,7 +10805,7 @@
         <v>0</v>
       </c>
       <c r="I38" t="n">
-        <v>120.6470157237802</v>
+        <v>23.09716008179447</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -10817,7 +10817,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>213.828673099982</v>
+        <v>388.259449250357</v>
       </c>
       <c r="N38" t="n">
         <v>318.7219932457141</v>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>76.88092050838969</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
         <v>294.54111633436</v>
@@ -11042,7 +11042,7 @@
         <v>0</v>
       </c>
       <c r="I41" t="n">
-        <v>0</v>
+        <v>120.6470157237802</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -11127,7 +11127,7 @@
         <v>57.34518285992368</v>
       </c>
       <c r="K42" t="n">
-        <v>23.73268658839821</v>
+        <v>0</v>
       </c>
       <c r="L42" t="n">
         <v>0</v>
@@ -11136,10 +11136,10 @@
         <v>0</v>
       </c>
       <c r="N42" t="n">
-        <v>361.1491563080032</v>
+        <v>292.3841435659339</v>
       </c>
       <c r="O42" t="n">
-        <v>162.1248995396916</v>
+        <v>28.12489953966606</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -11291,7 +11291,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>194.259449250334</v>
+        <v>195.1001687544331</v>
       </c>
       <c r="N44" t="n">
         <v>140.7704353309797</v>
@@ -11361,25 +11361,25 @@
         <v>17.72758189252907</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>184.3451828599819</v>
       </c>
       <c r="K45" t="n">
         <v>155.0164145241665</v>
       </c>
       <c r="L45" t="n">
-        <v>88.37717365633642</v>
+        <v>10.78470639412835</v>
       </c>
       <c r="M45" t="n">
-        <v>264.2997782656013</v>
+        <v>70.29977826558012</v>
       </c>
       <c r="N45" t="n">
-        <v>354.1491563080353</v>
+        <v>227.1491563079766</v>
       </c>
       <c r="O45" t="n">
-        <v>0</v>
+        <v>85.66895250304231</v>
       </c>
       <c r="P45" t="n">
-        <v>14.7120846843852</v>
+        <v>141.7120846844439</v>
       </c>
       <c r="Q45" t="n">
         <v>0</v>
@@ -22803,10 +22803,10 @@
         <v>71.60279091790068</v>
       </c>
       <c r="T5" t="n">
-        <v>67.92482594966785</v>
+        <v>179.7864259496693</v>
       </c>
       <c r="U5" t="n">
-        <v>246.1502211717261</v>
+        <v>134.2886211717247</v>
       </c>
       <c r="V5" t="n">
         <v>99.85102416682369</v>
@@ -22940,19 +22940,19 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>55.16107041894321</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>107.1999441241438</v>
       </c>
       <c r="O7" t="n">
-        <v>104.6153392778326</v>
+        <v>69.25432473474567</v>
       </c>
       <c r="P7" t="n">
         <v>109.2481596233592</v>
       </c>
       <c r="Q7" t="n">
-        <v>289.4682664255979</v>
+        <v>162.4682664255978</v>
       </c>
       <c r="R7" t="n">
         <v>178.6830132270525</v>
@@ -23040,10 +23040,10 @@
         <v>69.60279091789988</v>
       </c>
       <c r="T8" t="n">
-        <v>177.7864259496685</v>
+        <v>54.47442594966576</v>
       </c>
       <c r="U8" t="n">
-        <v>120.8382211717226</v>
+        <v>244.1502211717253</v>
       </c>
       <c r="V8" t="n">
         <v>84.85102416682292</v>
@@ -23177,13 +23177,13 @@
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>35.04901454307547</v>
       </c>
       <c r="N10" t="n">
-        <v>105.199944124143</v>
+        <v>0</v>
       </c>
       <c r="O10" t="n">
-        <v>108.9649951536842</v>
+        <v>179.1159247347517</v>
       </c>
       <c r="P10" t="n">
         <v>94.24815962335848</v>
@@ -23280,7 +23280,7 @@
         <v>242.7864259496674</v>
       </c>
       <c r="U11" t="n">
-        <v>164.6990211717221</v>
+        <v>145.1502211717242</v>
       </c>
       <c r="V11" t="n">
         <v>125.8510241668219</v>
@@ -23289,7 +23289,7 @@
         <v>134.3734759809455</v>
       </c>
       <c r="X11" t="n">
-        <v>88.28183346066569</v>
+        <v>107.8306334606636</v>
       </c>
       <c r="Y11" t="n">
         <v>171.3174326828044</v>
@@ -23411,13 +23411,13 @@
         <v>0</v>
       </c>
       <c r="L13" t="n">
-        <v>24.29789045285913</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>118.1610704189413</v>
+        <v>13.43604385332952</v>
       </c>
       <c r="N13" t="n">
-        <v>25.74874412412899</v>
+        <v>170.1999441241419</v>
       </c>
       <c r="O13" t="n">
         <v>80.11592473475062</v>
@@ -23432,7 +23432,7 @@
         <v>204.6830132270507</v>
       </c>
       <c r="S13" t="n">
-        <v>15.42828298154197</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
         <v>0</v>
@@ -23514,7 +23514,7 @@
         <v>119.6027909178988</v>
       </c>
       <c r="T14" t="n">
-        <v>63.7864259496674</v>
+        <v>227.7864259496674</v>
       </c>
       <c r="U14" t="n">
         <v>130.1502211717242</v>
@@ -23523,10 +23523,10 @@
         <v>110.8510241668219</v>
       </c>
       <c r="W14" t="n">
-        <v>138.9222759809194</v>
+        <v>119.3734759809455</v>
       </c>
       <c r="X14" t="n">
-        <v>237.2818334606657</v>
+        <v>92.83063346063955</v>
       </c>
       <c r="Y14" t="n">
         <v>156.3174326828044</v>
@@ -23542,7 +23542,7 @@
         <v>0</v>
       </c>
       <c r="C15" t="n">
-        <v>4.458331752568977</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -23608,7 +23608,7 @@
         <v>0</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>4.458331752568967</v>
       </c>
     </row>
     <row r="16">
@@ -23654,13 +23654,13 @@
         <v>103.1610704189413</v>
       </c>
       <c r="N16" t="n">
-        <v>155.1999441241419</v>
+        <v>10.74874412411569</v>
       </c>
       <c r="O16" t="n">
-        <v>84.66472473472447</v>
+        <v>65.11592473475062</v>
       </c>
       <c r="P16" t="n">
-        <v>120.2481596233574</v>
+        <v>284.2481596233574</v>
       </c>
       <c r="Q16" t="n">
         <v>173.4682664255959</v>
@@ -23754,16 +23754,16 @@
         <v>11.78642594966564</v>
       </c>
       <c r="U17" t="n">
-        <v>242.1502211717234</v>
+        <v>78.15022117172248</v>
       </c>
       <c r="V17" t="n">
         <v>58.85102416682011</v>
       </c>
       <c r="W17" t="n">
-        <v>67.37347598094377</v>
+        <v>86.9222759808888</v>
       </c>
       <c r="X17" t="n">
-        <v>40.83063346060896</v>
+        <v>185.2818334606649</v>
       </c>
       <c r="Y17" t="n">
         <v>104.3174326828035</v>
@@ -23988,19 +23988,19 @@
         <v>67.60279091789909</v>
       </c>
       <c r="T20" t="n">
-        <v>4.786425949664789</v>
+        <v>175.7864259496677</v>
       </c>
       <c r="U20" t="n">
-        <v>242.1502211717246</v>
+        <v>71.15022117172157</v>
       </c>
       <c r="V20" t="n">
-        <v>51.85102416681926</v>
+        <v>51.8510241668192</v>
       </c>
       <c r="W20" t="n">
-        <v>60.37347598094291</v>
+        <v>60.37347598094286</v>
       </c>
       <c r="X20" t="n">
-        <v>34.66503346057576</v>
+        <v>34.66503346057547</v>
       </c>
       <c r="Y20" t="n">
         <v>104.3174326828047</v>
@@ -24125,22 +24125,22 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>3.744214542973729</v>
+        <v>3.744214542973509</v>
       </c>
       <c r="N22" t="n">
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>177.1159247347509</v>
+        <v>6.115924734747949</v>
       </c>
       <c r="P22" t="n">
-        <v>61.24815962335481</v>
+        <v>61.24815962335475</v>
       </c>
       <c r="Q22" t="n">
-        <v>114.4682664255934</v>
+        <v>114.4682664255933</v>
       </c>
       <c r="R22" t="n">
-        <v>130.6830132270481</v>
+        <v>301.683013227051</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -24465,7 +24465,7 @@
         <v>296.7864259496666</v>
       </c>
       <c r="U26" t="n">
-        <v>212.5334211716763</v>
+        <v>192.1502211717178</v>
       </c>
       <c r="V26" t="n">
         <v>172.8510241668154</v>
@@ -24474,7 +24474,7 @@
         <v>181.3734759809391</v>
       </c>
       <c r="X26" t="n">
-        <v>135.2818334606593</v>
+        <v>155.6650334606178</v>
       </c>
       <c r="Y26" t="n">
         <v>225.3174326828035</v>
@@ -24502,7 +24502,7 @@
         <v>53.63624233787402</v>
       </c>
       <c r="G27" t="n">
-        <v>39.26417738444405</v>
+        <v>39.26417738445126</v>
       </c>
       <c r="H27" t="n">
         <v>41.57712492226734</v>
@@ -24544,10 +24544,10 @@
         <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>114.1790861752782</v>
+        <v>56.37716600066823</v>
       </c>
       <c r="V27" t="n">
-        <v>70.7087470169145</v>
+        <v>128.5106671915173</v>
       </c>
       <c r="W27" t="n">
         <v>0</v>
@@ -24833,22 +24833,22 @@
         <v>0</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>21.29789045285992</v>
       </c>
       <c r="M31" t="n">
         <v>115.1610704189421</v>
       </c>
       <c r="N31" t="n">
-        <v>37.88103457691079</v>
+        <v>167.1999441241427</v>
       </c>
       <c r="O31" t="n">
-        <v>70.11592473474408</v>
+        <v>90.49912473465963</v>
       </c>
       <c r="P31" t="n">
         <v>125.2481596233509</v>
       </c>
       <c r="Q31" t="n">
-        <v>349.4682664255968</v>
+        <v>178.4682664255894</v>
       </c>
       <c r="R31" t="n">
         <v>194.6830132270441</v>
@@ -25179,16 +25179,16 @@
         <v>33.15022117170929</v>
       </c>
       <c r="V35" t="n">
-        <v>13.85102416680692</v>
+        <v>136.2095162598442</v>
       </c>
       <c r="W35" t="n">
         <v>22.37347598093058</v>
       </c>
       <c r="X35" t="n">
-        <v>110.2818334606671</v>
+        <v>0</v>
       </c>
       <c r="Y35" t="n">
-        <v>12.07665863237008</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -25720,13 +25720,13 @@
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>133.7326727638296</v>
+        <v>251.759872764069</v>
       </c>
       <c r="S42" t="n">
         <v>191.7344244929049</v>
       </c>
       <c r="T42" t="n">
-        <v>137.4417369156188</v>
+        <v>19.41453691537936</v>
       </c>
       <c r="U42" t="n">
         <v>134.1790861752729</v>
@@ -25784,19 +25784,19 @@
         <v>0</v>
       </c>
       <c r="M43" t="n">
-        <v>58.16107041890925</v>
+        <v>192.1610704189347</v>
       </c>
       <c r="N43" t="n">
-        <v>185.4354862017231</v>
+        <v>244.1999441241353</v>
       </c>
       <c r="O43" t="n">
         <v>318.1159247347441</v>
       </c>
       <c r="P43" t="n">
-        <v>373.2481596233508</v>
+        <v>314.4837017009387</v>
       </c>
       <c r="Q43" t="n">
-        <v>426.4682664255895</v>
+        <v>292.468266425564</v>
       </c>
       <c r="R43" t="n">
         <v>308.6830132270188</v>
@@ -26110,7 +26110,7 @@
         <v>3</v>
       </c>
       <c r="B5" t="n">
-        <v>2489130.211598362</v>
+        <v>2489130.211598363</v>
       </c>
     </row>
     <row r="6">
@@ -26118,7 +26118,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="n">
-        <v>3084088.65805611</v>
+        <v>3084088.658056111</v>
       </c>
     </row>
     <row r="7">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>8951040.975658998</v>
+        <v>8951040.975658996</v>
       </c>
     </row>
   </sheetData>
@@ -26272,7 +26272,7 @@
         <v>1433440.04683612</v>
       </c>
       <c r="C2" t="n">
-        <v>1434871.296207826</v>
+        <v>1434871.296207827</v>
       </c>
       <c r="D2" t="n">
         <v>1443894.148536712</v>
@@ -26296,7 +26296,7 @@
         <v>1224445.477575746</v>
       </c>
       <c r="K2" t="n">
-        <v>1358159.54997429</v>
+        <v>1358159.549974291</v>
       </c>
       <c r="L2" t="n">
         <v>1529561.124537789</v>
@@ -26308,10 +26308,10 @@
         <v>1518023.138388425</v>
       </c>
       <c r="O2" t="n">
-        <v>1151012.902497684</v>
+        <v>1151012.902497683</v>
       </c>
       <c r="P2" t="n">
-        <v>943465.571245739</v>
+        <v>943465.5712457391</v>
       </c>
     </row>
     <row r="3">
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>613150.8721018791</v>
+        <v>613146.3936070916</v>
       </c>
       <c r="C4" t="n">
-        <v>611704.717947735</v>
+        <v>611700.2290693882</v>
       </c>
       <c r="D4" t="n">
-        <v>613265.5861605824</v>
+        <v>613261.0785285194</v>
       </c>
       <c r="E4" t="n">
-        <v>563459.1124260554</v>
+        <v>563455.3091935127</v>
       </c>
       <c r="F4" t="n">
-        <v>577343.2275220295</v>
+        <v>577339.188572149</v>
       </c>
       <c r="G4" t="n">
-        <v>613773.8976842635</v>
+        <v>613769.286182833</v>
       </c>
       <c r="H4" t="n">
-        <v>613292.6321475846</v>
+        <v>613287.9950131229</v>
       </c>
       <c r="I4" t="n">
-        <v>641153.0175808189</v>
+        <v>641147.9320952971</v>
       </c>
       <c r="J4" t="n">
-        <v>493931.4901830973</v>
+        <v>493928.5767172863</v>
       </c>
       <c r="K4" t="n">
-        <v>556852.6520393325</v>
+        <v>556848.7641958515</v>
       </c>
       <c r="L4" t="n">
-        <v>637133.2867446612</v>
+        <v>637128.1556935208</v>
       </c>
       <c r="M4" t="n">
-        <v>629495.9139261344</v>
+        <v>629490.8466230325</v>
       </c>
       <c r="N4" t="n">
-        <v>627180.5814278496</v>
+        <v>627175.5141247477</v>
       </c>
       <c r="O4" t="n">
-        <v>451164.5912298418</v>
+        <v>451161.868547769</v>
       </c>
       <c r="P4" t="n">
-        <v>365158.0167054267</v>
+        <v>365153.8331190746</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>512175.0367342405</v>
+        <v>512179.5152290285</v>
       </c>
       <c r="C6" t="n">
-        <v>775947.3712600913</v>
+        <v>775951.8601384383</v>
       </c>
       <c r="D6" t="n">
-        <v>777074.8173761296</v>
+        <v>777079.3250081928</v>
       </c>
       <c r="E6" t="n">
-        <v>463367.5812585146</v>
+        <v>463371.3844910573</v>
       </c>
       <c r="F6" t="n">
-        <v>745017.603349714</v>
+        <v>745021.642299594</v>
       </c>
       <c r="G6" t="n">
-        <v>752038.4637244568</v>
+        <v>752043.0752258874</v>
       </c>
       <c r="H6" t="n">
-        <v>795477.715557141</v>
+        <v>795482.3526916029</v>
       </c>
       <c r="I6" t="n">
-        <v>778869.933779909</v>
+        <v>778875.0192654307</v>
       </c>
       <c r="J6" t="n">
-        <v>518455.6533926488</v>
+        <v>518458.5668584593</v>
       </c>
       <c r="K6" t="n">
-        <v>699656.6309349579</v>
+        <v>699660.5187784391</v>
       </c>
       <c r="L6" t="n">
-        <v>683082.3797931281</v>
+        <v>683087.5108442687</v>
       </c>
       <c r="M6" t="n">
-        <v>834240.9664622842</v>
+        <v>834246.0337653863</v>
       </c>
       <c r="N6" t="n">
-        <v>837356.298960575</v>
+        <v>837361.3662636774</v>
       </c>
       <c r="O6" t="n">
-        <v>664520.9572678418</v>
+        <v>664523.6799499143</v>
       </c>
       <c r="P6" t="n">
-        <v>549458.7685403124</v>
+        <v>549462.9521266646</v>
       </c>
     </row>
   </sheetData>
@@ -27454,13 +27454,13 @@
         <v>402.0000000000005</v>
       </c>
       <c r="I2" t="n">
-        <v>115.8294913409761</v>
+        <v>236.4765070647563</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>12.95934199441454</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -27472,16 +27472,16 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>12.95934199441453</v>
       </c>
       <c r="P2" t="n">
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>67.38548829121267</v>
+        <v>76.88092050838992</v>
       </c>
       <c r="R2" t="n">
-        <v>402.0000000000005</v>
+        <v>271.857552059043</v>
       </c>
       <c r="S2" t="n">
         <v>402</v>
@@ -27691,7 +27691,7 @@
         <v>403.0000000000001</v>
       </c>
       <c r="I5" t="n">
-        <v>115.8294913409761</v>
+        <v>127.6577634113561</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
@@ -27706,7 +27706,7 @@
         <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>271.3928807102263</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -27718,7 +27718,7 @@
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>347.4250787377837</v>
+        <v>195.0699907880934</v>
       </c>
       <c r="S5" t="n">
         <v>403.0000000000001</v>
@@ -27758,7 +27758,7 @@
         <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>403.0000000000001</v>
+        <v>354.8464970541968</v>
       </c>
       <c r="F6" t="n">
         <v>403.0000000000001</v>
@@ -27767,13 +27767,13 @@
         <v>403.0000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>358.4551042880626</v>
+        <v>403.0000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>218.4874583499153</v>
       </c>
       <c r="J6" t="n">
-        <v>57.34518285992402</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
         <v>0</v>
@@ -27782,7 +27782,7 @@
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>264.2997782656032</v>
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -27818,7 +27818,7 @@
         <v>403.0000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>399.3913927661343</v>
+        <v>403.0000000000001</v>
       </c>
     </row>
     <row r="7">
@@ -27852,7 +27852,7 @@
         <v>186.9950388498149</v>
       </c>
       <c r="J7" t="n">
-        <v>7.093260311317607</v>
+        <v>141.293576610545</v>
       </c>
       <c r="K7" t="n">
         <v>242.2194623257332</v>
@@ -27925,10 +27925,10 @@
         <v>405.0000000000009</v>
       </c>
       <c r="H8" t="n">
-        <v>398.9108999095575</v>
+        <v>405.0000000000009</v>
       </c>
       <c r="I8" t="n">
-        <v>115.8294913409761</v>
+        <v>236.4765070647563</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27943,7 +27943,7 @@
         <v>0</v>
       </c>
       <c r="N8" t="n">
-        <v>235.5686757011245</v>
+        <v>0</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -27955,7 +27955,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>246.2429882767133</v>
+        <v>385.6212234558345</v>
       </c>
       <c r="S8" t="n">
         <v>405.0000000000009</v>
@@ -27992,16 +27992,16 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>352.4870831879495</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E9" t="n">
+        <v>342.6720972219126</v>
+      </c>
+      <c r="F9" t="n">
+        <v>392.1414764527964</v>
+      </c>
+      <c r="G9" t="n">
         <v>405.0000000000009</v>
-      </c>
-      <c r="F9" t="n">
-        <v>405.0000000000009</v>
-      </c>
-      <c r="G9" t="n">
-        <v>325.2641773844613</v>
       </c>
       <c r="H9" t="n">
         <v>405.0000000000009</v>
@@ -28010,7 +28010,7 @@
         <v>218.4874583499153</v>
       </c>
       <c r="J9" t="n">
-        <v>57.34518285992402</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -28083,10 +28083,10 @@
         <v>244.6453482513661</v>
       </c>
       <c r="H10" t="n">
-        <v>269.2974879778272</v>
+        <v>225.2278801999793</v>
       </c>
       <c r="I10" t="n">
-        <v>326.9950388498149</v>
+        <v>186.9950388498149</v>
       </c>
       <c r="J10" t="n">
         <v>281.2935766105451</v>
@@ -28119,10 +28119,10 @@
         <v>405.0000000000009</v>
       </c>
       <c r="T10" t="n">
-        <v>208.3217796210118</v>
+        <v>348.3217796210118</v>
       </c>
       <c r="U10" t="n">
-        <v>150.9366535695399</v>
+        <v>195.0062613473879</v>
       </c>
       <c r="V10" t="n">
         <v>199.1703102162162</v>
@@ -28165,10 +28165,10 @@
         <v>340.000000000002</v>
       </c>
       <c r="I11" t="n">
-        <v>340.000000000002</v>
+        <v>115.8294913409761</v>
       </c>
       <c r="J11" t="n">
-        <v>45.35511497174321</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
         <v>0</v>
@@ -28177,10 +28177,10 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>308.9510377705761</v>
       </c>
       <c r="N11" t="n">
-        <v>32.33868568246722</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -28238,7 +28238,7 @@
         <v>340.000000000002</v>
       </c>
       <c r="G12" t="n">
-        <v>340.0000000000019</v>
+        <v>340.000000000002</v>
       </c>
       <c r="H12" t="n">
         <v>340.000000000002</v>
@@ -28247,10 +28247,10 @@
         <v>340.000000000002</v>
       </c>
       <c r="J12" t="n">
-        <v>116.8330795361669</v>
+        <v>116.8330795361668</v>
       </c>
       <c r="K12" t="n">
-        <v>192.016414524109</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -28265,10 +28265,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>178.7120846843868</v>
       </c>
       <c r="Q12" t="n">
-        <v>293.6753660943903</v>
+        <v>293.6753660943904</v>
       </c>
       <c r="R12" t="n">
         <v>340.000000000002</v>
@@ -28302,10 +28302,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>333.6140336631249</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C13" t="n">
-        <v>340.000000000002</v>
+        <v>331.2758098501299</v>
       </c>
       <c r="D13" t="n">
         <v>340.000000000002</v>
@@ -28323,13 +28323,13 @@
         <v>225.2278801999793</v>
       </c>
       <c r="I13" t="n">
-        <v>186.9950388498149</v>
+        <v>340.000000000002</v>
       </c>
       <c r="J13" t="n">
         <v>141.293576610545</v>
       </c>
       <c r="K13" t="n">
-        <v>340.000000000002</v>
+        <v>242.2194623257332</v>
       </c>
       <c r="L13" t="n">
         <v>340.000000000002</v>
@@ -28402,7 +28402,7 @@
         <v>355.000000000002</v>
       </c>
       <c r="I14" t="n">
-        <v>236.4765070647563</v>
+        <v>115.8294913409761</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -28414,16 +28414,16 @@
         <v>23.79715577889442</v>
       </c>
       <c r="M14" t="n">
-        <v>95.97180787534626</v>
+        <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>184.796767580942</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>74.09463303262331</v>
       </c>
       <c r="P14" t="n">
-        <v>36.52795953816884</v>
+        <v>0</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -28487,10 +28487,10 @@
         <v>57.34518285992402</v>
       </c>
       <c r="K15" t="n">
-        <v>192.016414524109</v>
+        <v>120.9649390120002</v>
       </c>
       <c r="L15" t="n">
-        <v>103.7332308820211</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -28502,7 +28502,7 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>14.7120846843868</v>
+        <v>178.7120846843868</v>
       </c>
       <c r="Q15" t="n">
         <v>293.6753660943904</v>
@@ -28545,22 +28545,22 @@
         <v>355.000000000002</v>
       </c>
       <c r="D16" t="n">
-        <v>355.000000000002</v>
+        <v>285.5362180555555</v>
       </c>
       <c r="E16" t="n">
-        <v>355.000000000002</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F16" t="n">
         <v>274.3828559677419</v>
       </c>
       <c r="G16" t="n">
-        <v>244.6453482513661</v>
+        <v>355.000000000002</v>
       </c>
       <c r="H16" t="n">
         <v>225.2278801999793</v>
       </c>
       <c r="I16" t="n">
-        <v>239.0067542194801</v>
+        <v>186.9950388498149</v>
       </c>
       <c r="J16" t="n">
         <v>141.293576610545</v>
@@ -28593,19 +28593,19 @@
         <v>355.000000000002</v>
       </c>
       <c r="T16" t="n">
-        <v>208.3217796210118</v>
+        <v>245.1883851356419</v>
       </c>
       <c r="U16" t="n">
         <v>150.9366535695399</v>
       </c>
       <c r="V16" t="n">
-        <v>199.1703102162162</v>
+        <v>355.000000000002</v>
       </c>
       <c r="W16" t="n">
         <v>355.000000000002</v>
       </c>
       <c r="X16" t="n">
-        <v>355.000000000002</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y16" t="n">
         <v>355.000000000002</v>
@@ -28639,7 +28639,7 @@
         <v>407.0000000000028</v>
       </c>
       <c r="I17" t="n">
-        <v>272.6895147657817</v>
+        <v>115.8294913409761</v>
       </c>
       <c r="J17" t="n">
         <v>0</v>
@@ -28651,7 +28651,7 @@
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0</v>
+        <v>236.8786764293</v>
       </c>
       <c r="N17" t="n">
         <v>0</v>
@@ -28666,7 +28666,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>407.0000000000028</v>
+        <v>326.9813469955093</v>
       </c>
       <c r="S17" t="n">
         <v>407.0000000000028</v>
@@ -28703,22 +28703,22 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D18" t="n">
-        <v>347.9376868977026</v>
+        <v>407.0000000000028</v>
       </c>
       <c r="E18" t="n">
-        <v>364.5899648926722</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F18" t="n">
-        <v>407.0000000000028</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G18" t="n">
-        <v>407.0000000000028</v>
+        <v>325.2641773844613</v>
       </c>
       <c r="H18" t="n">
         <v>327.5771249222702</v>
       </c>
       <c r="I18" t="n">
-        <v>218.4874583499153</v>
+        <v>334.0008562804181</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -28751,7 +28751,7 @@
         <v>407.0000000000028</v>
       </c>
       <c r="T18" t="n">
-        <v>407.0000000000028</v>
+        <v>403.441736915627</v>
       </c>
       <c r="U18" t="n">
         <v>407.0000000000028</v>
@@ -28833,13 +28833,13 @@
         <v>208.3217796210118</v>
       </c>
       <c r="U19" t="n">
-        <v>314.9366535695409</v>
+        <v>150.9366535695399</v>
       </c>
       <c r="V19" t="n">
         <v>199.1703102162162</v>
       </c>
       <c r="W19" t="n">
-        <v>226.3728098387097</v>
+        <v>390.3728098387106</v>
       </c>
       <c r="X19" t="n">
         <v>247.4436454301076</v>
@@ -28876,7 +28876,7 @@
         <v>407.0000000000017</v>
       </c>
       <c r="I20" t="n">
-        <v>293.1918649003504</v>
+        <v>262.64618960813</v>
       </c>
       <c r="J20" t="n">
         <v>0</v>
@@ -28958,7 +28958,7 @@
         <v>218.4874583499153</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>57.34518285992402</v>
       </c>
       <c r="K21" t="n">
         <v>0</v>
@@ -29016,7 +29016,7 @@
         <v>407.0000000000017</v>
       </c>
       <c r="C22" t="n">
-        <v>407.0000000000017</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D22" t="n">
         <v>407.0000000000017</v>
@@ -29034,16 +29034,16 @@
         <v>225.2278801999793</v>
       </c>
       <c r="I22" t="n">
-        <v>357.9950388498178</v>
+        <v>332.2013191829342</v>
       </c>
       <c r="J22" t="n">
-        <v>229.0576411950721</v>
+        <v>141.293576610545</v>
       </c>
       <c r="K22" t="n">
         <v>242.2194623257332</v>
       </c>
       <c r="L22" t="n">
-        <v>407.0000000000017</v>
+        <v>364.2978904528611</v>
       </c>
       <c r="M22" t="n">
         <v>407.0000000000017</v>
@@ -29067,7 +29067,7 @@
         <v>355.428282981544</v>
       </c>
       <c r="T22" t="n">
-        <v>208.3217796210118</v>
+        <v>379.3217796210148</v>
       </c>
       <c r="U22" t="n">
         <v>150.9366535695399</v>
@@ -29076,13 +29076,13 @@
         <v>199.1703102162162</v>
       </c>
       <c r="W22" t="n">
-        <v>226.3728098387432</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X22" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y22" t="n">
-        <v>287.4653528494624</v>
+        <v>407.0000000000017</v>
       </c>
     </row>
     <row r="23">
@@ -29116,10 +29116,10 @@
         <v>405.000000000001</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>60.28822889015452</v>
       </c>
       <c r="K23" t="n">
-        <v>60.28822889015407</v>
+        <v>0</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -29174,13 +29174,13 @@
         <v>384.5565566463266</v>
       </c>
       <c r="C24" t="n">
-        <v>361.0999124455193</v>
+        <v>379.5593605294573</v>
       </c>
       <c r="D24" t="n">
-        <v>347.9376868977026</v>
+        <v>405.000000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>342.6720972219126</v>
+        <v>405.000000000001</v>
       </c>
       <c r="F24" t="n">
         <v>339.6362423378769</v>
@@ -29189,7 +29189,7 @@
         <v>325.2641773844613</v>
       </c>
       <c r="H24" t="n">
-        <v>327.5771249222702</v>
+        <v>405.000000000001</v>
       </c>
       <c r="I24" t="n">
         <v>218.4874583499153</v>
@@ -29216,7 +29216,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>345.7184748116732</v>
+        <v>129.6753660943903</v>
       </c>
       <c r="R24" t="n">
         <v>405.000000000001</v>
@@ -29225,10 +29225,10 @@
         <v>405.000000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>403.441736915627</v>
+        <v>405.000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>400.1790861752811</v>
+        <v>405.000000000001</v>
       </c>
       <c r="V24" t="n">
         <v>405.000000000001</v>
@@ -29240,7 +29240,7 @@
         <v>405.000000000001</v>
       </c>
       <c r="Y24" t="n">
-        <v>405.000000000001</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="25">
@@ -29250,16 +29250,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>405.000000000001</v>
+        <v>396.0604323145695</v>
       </c>
       <c r="C25" t="n">
-        <v>405.000000000001</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D25" t="n">
         <v>405.000000000001</v>
       </c>
       <c r="E25" t="n">
-        <v>405.000000000001</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F25" t="n">
         <v>405.000000000001</v>
@@ -29268,7 +29268,7 @@
         <v>244.6453482513661</v>
       </c>
       <c r="H25" t="n">
-        <v>405.000000000001</v>
+        <v>225.2278801999793</v>
       </c>
       <c r="I25" t="n">
         <v>164.6487343086428</v>
@@ -29277,7 +29277,7 @@
         <v>7.093260311317607</v>
       </c>
       <c r="K25" t="n">
-        <v>281.2820174718565</v>
+        <v>405.000000000001</v>
       </c>
       <c r="L25" t="n">
         <v>405.000000000001</v>
@@ -29307,19 +29307,19 @@
         <v>208.3217796210118</v>
       </c>
       <c r="U25" t="n">
-        <v>150.9366535695399</v>
+        <v>405.000000000001</v>
       </c>
       <c r="V25" t="n">
-        <v>199.1703102162162</v>
+        <v>405.000000000001</v>
       </c>
       <c r="W25" t="n">
+        <v>226.3728098387097</v>
+      </c>
+      <c r="X25" t="n">
         <v>405.000000000001</v>
       </c>
-      <c r="X25" t="n">
-        <v>247.4436454301076</v>
-      </c>
       <c r="Y25" t="n">
-        <v>405.000000000001</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="26">
@@ -29350,22 +29350,22 @@
         <v>286.0000000000028</v>
       </c>
       <c r="I26" t="n">
-        <v>236.4765070647563</v>
+        <v>286.0000000000028</v>
       </c>
       <c r="J26" t="n">
         <v>0</v>
       </c>
       <c r="K26" t="n">
-        <v>57.98681909547736</v>
+        <v>0</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
       </c>
       <c r="M26" t="n">
+        <v>159.4300088888581</v>
+      </c>
+      <c r="N26" t="n">
         <v>286.0000000000028</v>
-      </c>
-      <c r="N26" t="n">
-        <v>161.4921769440304</v>
       </c>
       <c r="O26" t="n">
         <v>0</v>
@@ -29441,16 +29441,16 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>286.0000000000028</v>
       </c>
       <c r="N27" t="n">
-        <v>227.1491563079784</v>
+        <v>286.0000000000028</v>
       </c>
       <c r="O27" t="n">
-        <v>139.3786330749446</v>
+        <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>185.7120846843924</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>286.0000000000028</v>
@@ -29490,7 +29490,7 @@
         <v>286.0000000000028</v>
       </c>
       <c r="C28" t="n">
-        <v>286.0000000000028</v>
+        <v>272.7252466480447</v>
       </c>
       <c r="D28" t="n">
         <v>286.0000000000028</v>
@@ -29511,7 +29511,7 @@
         <v>286.0000000000028</v>
       </c>
       <c r="J28" t="n">
-        <v>147.9741599556325</v>
+        <v>286.0000000000028</v>
       </c>
       <c r="K28" t="n">
         <v>286.0000000000028</v>
@@ -29544,7 +29544,7 @@
         <v>286.0000000000028</v>
       </c>
       <c r="U28" t="n">
-        <v>286.0000000000028</v>
+        <v>161.2489133075906</v>
       </c>
       <c r="V28" t="n">
         <v>286.0000000000028</v>
@@ -29587,19 +29587,19 @@
         <v>343.0000000000012</v>
       </c>
       <c r="I29" t="n">
-        <v>236.4765070647563</v>
+        <v>115.8294913409761</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
       </c>
       <c r="K29" t="n">
-        <v>57.98681909547736</v>
+        <v>0</v>
       </c>
       <c r="L29" t="n">
         <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>296.3251322964913</v>
       </c>
       <c r="N29" t="n">
         <v>0</v>
@@ -29611,7 +29611,7 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>131.2192892592272</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
         <v>343.0000000000012</v>
@@ -29681,16 +29681,16 @@
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>229.8771656154119</v>
+        <v>227.1491563079784</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>199.1248995396741</v>
       </c>
       <c r="P30" t="n">
         <v>185.7120846843941</v>
       </c>
       <c r="Q30" t="n">
-        <v>300.6753660943976</v>
+        <v>129.6753660943903</v>
       </c>
       <c r="R30" t="n">
         <v>343.0000000000012</v>
@@ -29724,7 +29724,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>287.1138003370787</v>
+        <v>343.0000000000012</v>
       </c>
       <c r="C31" t="n">
         <v>272.7252466480447</v>
@@ -29733,16 +29733,16 @@
         <v>343.0000000000012</v>
       </c>
       <c r="E31" t="n">
-        <v>280.9809048369565</v>
+        <v>321.7368020247491</v>
       </c>
       <c r="F31" t="n">
         <v>343.0000000000012</v>
       </c>
       <c r="G31" t="n">
-        <v>309.3844820096726</v>
+        <v>343.0000000000012</v>
       </c>
       <c r="H31" t="n">
-        <v>343.0000000000012</v>
+        <v>225.2278801999793</v>
       </c>
       <c r="I31" t="n">
         <v>186.9950388498149</v>
@@ -29751,7 +29751,7 @@
         <v>141.293576610545</v>
       </c>
       <c r="K31" t="n">
-        <v>343.0000000000012</v>
+        <v>242.2194623257332</v>
       </c>
       <c r="L31" t="n">
         <v>343.0000000000012</v>
@@ -29784,7 +29784,7 @@
         <v>150.9366535695399</v>
       </c>
       <c r="V31" t="n">
-        <v>199.1703102162162</v>
+        <v>343.0000000000012</v>
       </c>
       <c r="W31" t="n">
         <v>343.0000000000012</v>
@@ -29793,7 +29793,7 @@
         <v>343.0000000000012</v>
       </c>
       <c r="Y31" t="n">
-        <v>343.0000000000012</v>
+        <v>287.4653528494624</v>
       </c>
     </row>
     <row r="32">
@@ -29812,7 +29812,7 @@
         <v>410.3391557398498</v>
       </c>
       <c r="E32" t="n">
-        <v>482.0000000000001</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F32" t="n">
         <v>404.8896287080119</v>
@@ -29839,7 +29839,7 @@
         <v>0</v>
       </c>
       <c r="N32" t="n">
-        <v>164.0488873885579</v>
+        <v>241.6855977816893</v>
       </c>
       <c r="O32" t="n">
         <v>0</v>
@@ -29888,10 +29888,10 @@
         <v>361.0999124455193</v>
       </c>
       <c r="D33" t="n">
-        <v>360.1580544209975</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E33" t="n">
-        <v>342.6720972219126</v>
+        <v>379.1580402522944</v>
       </c>
       <c r="F33" t="n">
         <v>339.6362423378769</v>
@@ -29933,7 +29933,7 @@
         <v>482.0000000000001</v>
       </c>
       <c r="S33" t="n">
-        <v>482.0000000000001</v>
+        <v>457.7344244929132</v>
       </c>
       <c r="T33" t="n">
         <v>403.441736915627</v>
@@ -30043,7 +30043,7 @@
         <v>482.0000000000006</v>
       </c>
       <c r="C35" t="n">
-        <v>449.4745782429939</v>
+        <v>478.37025545682</v>
       </c>
       <c r="D35" t="n">
         <v>410.3391557398498</v>
@@ -30073,7 +30073,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>193.8654995736057</v>
+        <v>174.4307761503871</v>
       </c>
       <c r="N35" t="n">
         <v>0</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>223.9656680019195</v>
+        <v>195.0699907880934</v>
       </c>
       <c r="S35" t="n">
         <v>482.0000000000006</v>
@@ -30185,7 +30185,7 @@
         <v>432.3731429098285</v>
       </c>
       <c r="X36" t="n">
-        <v>419.8627394453875</v>
+        <v>456.348682475769</v>
       </c>
       <c r="Y36" t="n">
         <v>399.3913927661343</v>
@@ -30198,7 +30198,7 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>399.2890123236357</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C37" t="n">
         <v>272.7252466480447</v>
@@ -30213,7 +30213,7 @@
         <v>274.3828559677419</v>
       </c>
       <c r="G37" t="n">
-        <v>244.6453482513661</v>
+        <v>356.8205602379232</v>
       </c>
       <c r="H37" t="n">
         <v>225.2278801999793</v>
@@ -30298,7 +30298,7 @@
         <v>398.9108999095575</v>
       </c>
       <c r="I38" t="n">
-        <v>115.829491340976</v>
+        <v>213.3793469829618</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -30310,7 +30310,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>174.430776150375</v>
+        <v>0</v>
       </c>
       <c r="N38" t="n">
         <v>0</v>
@@ -30322,7 +30322,7 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>76.88092050838969</v>
       </c>
       <c r="R38" t="n">
         <v>195.0699907880933</v>
@@ -30419,13 +30419,13 @@
         <v>414.5106671915202</v>
       </c>
       <c r="W39" t="n">
-        <v>468.8590859402085</v>
+        <v>432.3731429098285</v>
       </c>
       <c r="X39" t="n">
         <v>419.8627394453875</v>
       </c>
       <c r="Y39" t="n">
-        <v>399.3913927661343</v>
+        <v>435.8773357965143</v>
       </c>
     </row>
     <row r="40">
@@ -30441,7 +30441,7 @@
         <v>272.7252466480447</v>
       </c>
       <c r="D40" t="n">
-        <v>419.5362180555774</v>
+        <v>419.5362180556227</v>
       </c>
       <c r="E40" t="n">
         <v>280.9809048369565</v>
@@ -30465,7 +30465,7 @@
         <v>242.2194623257331</v>
       </c>
       <c r="L40" t="n">
-        <v>476.4731024393737</v>
+        <v>476.4731024393284</v>
       </c>
       <c r="M40" t="n">
         <v>482.0000000000019</v>
@@ -30535,7 +30535,7 @@
         <v>266.0000000000082</v>
       </c>
       <c r="I41" t="n">
-        <v>236.4765070647561</v>
+        <v>115.8294913409758</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -30620,7 +30620,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>83.65682313734517</v>
+        <v>162.0164145241338</v>
       </c>
       <c r="L42" t="n">
         <v>144.7847063941547</v>
@@ -30635,10 +30635,10 @@
         <v>0</v>
       </c>
       <c r="P42" t="n">
-        <v>14.71208468438611</v>
+        <v>148.7120846844116</v>
       </c>
       <c r="Q42" t="n">
-        <v>129.67536609439</v>
+        <v>143.8134740380688</v>
       </c>
       <c r="R42" t="n">
         <v>266.0000000000082</v>
@@ -30784,7 +30784,7 @@
         <v>0</v>
       </c>
       <c r="M44" t="n">
-        <v>194.0000000000212</v>
+        <v>193.1592804959221</v>
       </c>
       <c r="N44" t="n">
         <v>194.0000000000212</v>
@@ -30854,7 +30854,7 @@
         <v>194.0000000000212</v>
       </c>
       <c r="J45" t="n">
-        <v>57.34518285992323</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
         <v>0</v>
@@ -30863,13 +30863,13 @@
         <v>0</v>
       </c>
       <c r="M45" t="n">
-        <v>0</v>
+        <v>194.0000000000212</v>
       </c>
       <c r="N45" t="n">
         <v>0</v>
       </c>
       <c r="O45" t="n">
-        <v>135.0764852408929</v>
+        <v>0</v>
       </c>
       <c r="P45" t="n">
         <v>0</v>
@@ -34746,7 +34746,7 @@
         <v>40.36241586546246</v>
       </c>
       <c r="K2" t="n">
-        <v>125.9725228989372</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L2" t="n">
         <v>127</v>
@@ -34758,7 +34758,7 @@
         <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>79.44464801384729</v>
+        <v>92.40399000826181</v>
       </c>
       <c r="P2" t="n">
         <v>127</v>
@@ -34977,7 +34977,7 @@
         <v>4.089100090442553</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>11.82827207038002</v>
       </c>
       <c r="J5" t="n">
         <v>40.36241586546246</v>
@@ -35001,7 +35001,7 @@
         <v>127.0000000000001</v>
       </c>
       <c r="Q5" t="n">
-        <v>11.82827207038002</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -35044,7 +35044,7 @@
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>60.32790277808749</v>
+        <v>12.17439983228414</v>
       </c>
       <c r="F6" t="n">
         <v>63.36375766212325</v>
@@ -35053,7 +35053,7 @@
         <v>77.73582261553881</v>
       </c>
       <c r="H6" t="n">
-        <v>30.87797936579236</v>
+        <v>75.42287507772993</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -35104,7 +35104,7 @@
         <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>3.608607233865769</v>
       </c>
     </row>
     <row r="7">
@@ -35211,7 +35211,7 @@
         <v>2.131069924039975</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>6.089100090443349</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -35220,7 +35220,7 @@
         <v>40.36241586546246</v>
       </c>
       <c r="K8" t="n">
-        <v>113.0131809045227</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L8" t="n">
         <v>140</v>
@@ -35241,7 +35241,7 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>51.17299748861986</v>
+        <v>45.08389739817647</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -35278,16 +35278,16 @@
         <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>4.54939629024681</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>62.32790277808829</v>
+        <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>65.36375766212404</v>
+        <v>52.50523411491955</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>79.7358226155396</v>
       </c>
       <c r="H9" t="n">
         <v>77.42287507773072</v>
@@ -35369,10 +35369,10 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>44.06960777784794</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>140.0000000000001</v>
+        <v>0</v>
       </c>
       <c r="J10" t="n">
         <v>140.0000000000001</v>
@@ -35405,10 +35405,10 @@
         <v>49.57171701845695</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>140.0000000000001</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>44.06960777784795</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -35451,10 +35451,10 @@
         <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>103.5234929352457</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>85.71753083720567</v>
+        <v>40.36241586546246</v>
       </c>
       <c r="K11" t="n">
         <v>113.0131809045226</v>
@@ -35463,7 +35463,7 @@
         <v>140.2028442211056</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>3.948598695080301</v>
       </c>
       <c r="N11" t="n">
         <v>0</v>
@@ -35478,7 +35478,7 @@
         <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>144.9300092119086</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -35533,10 +35533,10 @@
         <v>121.5125416500867</v>
       </c>
       <c r="J12" t="n">
-        <v>59.48789667624286</v>
+        <v>59.48789667624283</v>
       </c>
       <c r="K12" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -35551,7 +35551,7 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>164</v>
       </c>
       <c r="Q12" t="n">
         <v>164</v>
@@ -35588,10 +35588,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>46.50023332604625</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
-        <v>67.27475335195732</v>
+        <v>58.55056320208526</v>
       </c>
       <c r="D13" t="n">
         <v>54.46378194444651</v>
@@ -35609,13 +35609,13 @@
         <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>153.0049611501871</v>
       </c>
       <c r="J13" t="n">
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>97.78053767426877</v>
+        <v>0</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -35703,13 +35703,13 @@
         <v>0</v>
       </c>
       <c r="N14" t="n">
-        <v>37.56667349445449</v>
+        <v>0</v>
       </c>
       <c r="O14" t="n">
-        <v>79.44464801384729</v>
+        <v>153.5392810464706</v>
       </c>
       <c r="P14" t="n">
-        <v>164</v>
+        <v>127.4720404618312</v>
       </c>
       <c r="Q14" t="n">
         <v>0</v>
@@ -35773,22 +35773,22 @@
         <v>0</v>
       </c>
       <c r="K15" t="n">
+        <v>92.94852448789121</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
         <v>164</v>
-      </c>
-      <c r="L15" t="n">
-        <v>92.94852448789121</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
       </c>
       <c r="Q15" t="n">
         <v>164</v>
@@ -35831,22 +35831,22 @@
         <v>82.27475335195732</v>
       </c>
       <c r="D16" t="n">
-        <v>69.46378194444651</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
-        <v>74.01909516304545</v>
+        <v>0</v>
       </c>
       <c r="F16" t="n">
         <v>0</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>110.3546517486359</v>
       </c>
       <c r="H16" t="n">
         <v>0</v>
       </c>
       <c r="I16" t="n">
-        <v>52.01171536966522</v>
+        <v>0</v>
       </c>
       <c r="J16" t="n">
         <v>0</v>
@@ -35879,19 +35879,19 @@
         <v>0</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>36.86660551463005</v>
       </c>
       <c r="U16" t="n">
         <v>0</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>155.8296897837858</v>
       </c>
       <c r="W16" t="n">
         <v>128.6271901612923</v>
       </c>
       <c r="X16" t="n">
-        <v>107.5563545698944</v>
+        <v>0</v>
       </c>
       <c r="Y16" t="n">
         <v>67.53464715053963</v>
@@ -35925,7 +35925,7 @@
         <v>8.089100090445282</v>
       </c>
       <c r="I17" t="n">
-        <v>36.21300770102535</v>
+        <v>0</v>
       </c>
       <c r="J17" t="n">
         <v>40.36241586546246</v>
@@ -35952,7 +35952,7 @@
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>95.69834850639057</v>
+        <v>131.9113562074158</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -35989,22 +35989,22 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0</v>
+        <v>59.06231310230021</v>
       </c>
       <c r="E18" t="n">
-        <v>21.91786767075956</v>
+        <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>67.36375766212598</v>
+        <v>0</v>
       </c>
       <c r="G18" t="n">
-        <v>81.73582261554154</v>
+        <v>0</v>
       </c>
       <c r="H18" t="n">
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>115.5133979305028</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -36037,7 +36037,7 @@
         <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>3.558263084375819</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>6.820913824721755</v>
@@ -36119,13 +36119,13 @@
         <v>0</v>
       </c>
       <c r="U19" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
         <v>164.0000000000009</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -36162,7 +36162,7 @@
         <v>8.089100090444145</v>
       </c>
       <c r="I20" t="n">
-        <v>56.71535783559412</v>
+        <v>26.1696825433737</v>
       </c>
       <c r="J20" t="n">
         <v>40.36241586546246</v>
@@ -36174,7 +36174,7 @@
         <v>140.2028442211056</v>
       </c>
       <c r="M20" t="n">
-        <v>102.9131700890593</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -36189,7 +36189,7 @@
         <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>133.4588453812803</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -36302,7 +36302,7 @@
         <v>119.886199662923</v>
       </c>
       <c r="C22" t="n">
-        <v>134.274753351957</v>
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>121.4637819444462</v>
@@ -36320,16 +36320,16 @@
         <v>0</v>
       </c>
       <c r="I22" t="n">
-        <v>171.0000000000029</v>
+        <v>145.2062803331193</v>
       </c>
       <c r="J22" t="n">
-        <v>87.76406458452706</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>42.70210954714059</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
         <v>0</v>
@@ -36353,7 +36353,7 @@
         <v>0</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>171.000000000003</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -36362,13 +36362,13 @@
         <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>3.353187536839584e-11</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>0</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>119.5346471505393</v>
       </c>
     </row>
     <row r="23">
@@ -36399,25 +36399,25 @@
         <v>6.089100090443463</v>
       </c>
       <c r="I23" t="n">
-        <v>168.5234929352447</v>
+        <v>289.170508659025</v>
       </c>
       <c r="J23" t="n">
-        <v>40.36241586546246</v>
+        <v>100.650644755617</v>
       </c>
       <c r="K23" t="n">
-        <v>173.3014097946767</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L23" t="n">
         <v>140.2028442211056</v>
       </c>
       <c r="M23" t="n">
-        <v>13.20013176990528</v>
+        <v>111.1084680322814</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
       </c>
       <c r="O23" t="n">
-        <v>298.0000000000039</v>
+        <v>79.44464801384729</v>
       </c>
       <c r="P23" t="n">
         <v>127.4720404618312</v>
@@ -36460,13 +36460,13 @@
         <v>0</v>
       </c>
       <c r="C24" t="n">
-        <v>0</v>
+        <v>18.459448083938</v>
       </c>
       <c r="D24" t="n">
-        <v>0</v>
+        <v>57.06231310229839</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>62.3279027780884</v>
       </c>
       <c r="F24" t="n">
         <v>0</v>
@@ -36475,7 +36475,7 @@
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>77.42287507773084</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -36502,7 +36502,7 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>216.0431087172829</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36511,10 +36511,10 @@
         <v>0</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>1.558263084374</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>4.820913824719936</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -36526,7 +36526,7 @@
         <v>0</v>
       </c>
       <c r="Y24" t="n">
-        <v>5.608607233866678</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -36536,16 +36536,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>117.8861996629224</v>
+        <v>108.9466319774909</v>
       </c>
       <c r="C25" t="n">
-        <v>132.2747533519563</v>
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>119.4637819444455</v>
       </c>
       <c r="E25" t="n">
-        <v>124.0190951630445</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>130.6171440322591</v>
@@ -36554,7 +36554,7 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>179.7721198000218</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
         <v>0</v>
@@ -36563,7 +36563,7 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>39.06255514612329</v>
+        <v>162.7805376742678</v>
       </c>
       <c r="L25" t="n">
         <v>40.70210954713991</v>
@@ -36593,19 +36593,19 @@
         <v>0</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>254.0633464304611</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>205.8296897837848</v>
       </c>
       <c r="W25" t="n">
-        <v>178.6271901612913</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>157.5563545698935</v>
       </c>
       <c r="Y25" t="n">
-        <v>117.5346471505387</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -36636,22 +36636,22 @@
         <v>0</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>49.52349293524654</v>
       </c>
       <c r="J26" t="n">
         <v>40.36241586546246</v>
       </c>
       <c r="K26" t="n">
-        <v>171</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L26" t="n">
         <v>140.2028442211056</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>127.072286688988</v>
       </c>
       <c r="N26" t="n">
-        <v>27.67895131684777</v>
+        <v>0</v>
       </c>
       <c r="O26" t="n">
         <v>79.44464801384729</v>
@@ -36663,7 +36663,7 @@
         <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>90.93000921190941</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -36721,22 +36721,22 @@
         <v>171.0000000000056</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>30.70266810885369</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>21.7002217343997</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>58.85084369202443</v>
       </c>
       <c r="O27" t="n">
-        <v>111.2537335352778</v>
+        <v>171.0000000000056</v>
       </c>
       <c r="P27" t="n">
-        <v>171.0000000000056</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
         <v>156.3246339056125</v>
@@ -36776,7 +36776,7 @@
         <v>0</v>
       </c>
       <c r="C28" t="n">
-        <v>13.27475335195817</v>
+        <v>0</v>
       </c>
       <c r="D28" t="n">
         <v>0.4637819444473621</v>
@@ -36797,7 +36797,7 @@
         <v>99.00496115018795</v>
       </c>
       <c r="J28" t="n">
-        <v>6.680583345087488</v>
+        <v>144.7064233894579</v>
       </c>
       <c r="K28" t="n">
         <v>43.78053767426963</v>
@@ -36830,7 +36830,7 @@
         <v>77.67822037899103</v>
       </c>
       <c r="U28" t="n">
-        <v>135.0633464304629</v>
+        <v>10.31225973805071</v>
       </c>
       <c r="V28" t="n">
         <v>86.82968978378665</v>
@@ -36879,16 +36879,16 @@
         <v>40.36241586546246</v>
       </c>
       <c r="K29" t="n">
-        <v>171</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L29" t="n">
         <v>140.2028442211056</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>28.66577041236309</v>
       </c>
       <c r="N29" t="n">
-        <v>64.27059177795627</v>
+        <v>0</v>
       </c>
       <c r="O29" t="n">
         <v>79.44464801384729</v>
@@ -36897,10 +36897,10 @@
         <v>127.4720404618312</v>
       </c>
       <c r="Q29" t="n">
-        <v>54.33836875083728</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>147.9300092119078</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -36961,22 +36961,22 @@
         <v>0</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>2.728009307433506</v>
       </c>
       <c r="M30" t="n">
         <v>0</v>
       </c>
       <c r="N30" t="n">
-        <v>2.728009307433506</v>
+        <v>0</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>171.0000000000074</v>
       </c>
       <c r="P30" t="n">
         <v>171.0000000000074</v>
       </c>
       <c r="Q30" t="n">
-        <v>171.0000000000074</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
         <v>0</v>
@@ -37010,7 +37010,7 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0</v>
+        <v>55.88619966292254</v>
       </c>
       <c r="C31" t="n">
         <v>0</v>
@@ -37019,16 +37019,16 @@
         <v>57.46378194444571</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>40.75589718779261</v>
       </c>
       <c r="F31" t="n">
         <v>68.61714403225926</v>
       </c>
       <c r="G31" t="n">
-        <v>64.73913375830645</v>
+        <v>98.35465174863509</v>
       </c>
       <c r="H31" t="n">
-        <v>117.7721198000219</v>
+        <v>0</v>
       </c>
       <c r="I31" t="n">
         <v>0</v>
@@ -37037,7 +37037,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>100.780537674268</v>
+        <v>0</v>
       </c>
       <c r="L31" t="n">
         <v>0</v>
@@ -37070,7 +37070,7 @@
         <v>0</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>143.829689783785</v>
       </c>
       <c r="W31" t="n">
         <v>116.6271901612915</v>
@@ -37079,7 +37079,7 @@
         <v>95.55635456989364</v>
       </c>
       <c r="Y31" t="n">
-        <v>55.53464715053883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32">
@@ -37098,7 +37098,7 @@
         <v>0</v>
       </c>
       <c r="E32" t="n">
-        <v>77.63671039313147</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -37116,7 +37116,7 @@
         <v>40.36241586546246</v>
       </c>
       <c r="K32" t="n">
-        <v>113.0131809045227</v>
+        <v>113.0131809045226</v>
       </c>
       <c r="L32" t="n">
         <v>140.2028442211056</v>
@@ -37134,7 +37134,7 @@
         <v>127.4720404618312</v>
       </c>
       <c r="Q32" t="n">
-        <v>7.561003872877456</v>
+        <v>85.19771426600904</v>
       </c>
       <c r="R32" t="n">
         <v>0</v>
@@ -37174,10 +37174,10 @@
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>12.22036752329492</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>36.48594303038183</v>
       </c>
       <c r="F33" t="n">
         <v>0</v>
@@ -37219,7 +37219,7 @@
         <v>0</v>
       </c>
       <c r="S33" t="n">
-        <v>24.26557550708693</v>
+        <v>0</v>
       </c>
       <c r="T33" t="n">
         <v>0</v>
@@ -37329,7 +37329,7 @@
         <v>0.0006870444260584918</v>
       </c>
       <c r="C35" t="n">
-        <v>0</v>
+        <v>28.89567721382609</v>
       </c>
       <c r="D35" t="n">
         <v>0</v>
@@ -37374,7 +37374,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>28.89567721382606</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>7.397209082099781</v>
@@ -37432,7 +37432,7 @@
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>36.48594303038143</v>
+        <v>0</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
@@ -37471,7 +37471,7 @@
         <v>0</v>
       </c>
       <c r="X36" t="n">
-        <v>0</v>
+        <v>36.48594303038142</v>
       </c>
       <c r="Y36" t="n">
         <v>0</v>
@@ -37484,22 +37484,22 @@
         </is>
       </c>
       <c r="B37" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" t="n">
         <v>112.1752119865571</v>
-      </c>
-      <c r="C37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" t="n">
-        <v>0</v>
       </c>
       <c r="H37" t="n">
         <v>0</v>
@@ -37705,13 +37705,13 @@
         <v>0</v>
       </c>
       <c r="W39" t="n">
-        <v>36.48594303037999</v>
+        <v>0</v>
       </c>
       <c r="X39" t="n">
         <v>0</v>
       </c>
       <c r="Y39" t="n">
-        <v>0</v>
+        <v>36.48594303037997</v>
       </c>
     </row>
     <row r="40">
@@ -37721,13 +37721,13 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>134.0000000000225</v>
+        <v>134.0000000000219</v>
       </c>
       <c r="C40" t="n">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>134.0000000000219</v>
+        <v>134.00000000006</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
@@ -37751,7 +37751,7 @@
         <v>0</v>
       </c>
       <c r="L40" t="n">
-        <v>112.1752119865128</v>
+        <v>112.1752119864674</v>
       </c>
       <c r="M40" t="n">
         <v>23.83892958105872</v>
@@ -37906,7 +37906,7 @@
         <v>0</v>
       </c>
       <c r="K42" t="n">
-        <v>79.37309520163507</v>
+        <v>134.0000000000255</v>
       </c>
       <c r="L42" t="n">
         <v>134.0000000000255</v>
@@ -37915,16 +37915,16 @@
         <v>1.700221734405787</v>
       </c>
       <c r="N42" t="n">
+        <v>65.23498725795621</v>
+      </c>
+      <c r="O42" t="n">
+        <v>0</v>
+      </c>
+      <c r="P42" t="n">
         <v>134.0000000000255</v>
       </c>
-      <c r="O42" t="n">
-        <v>134.0000000000255</v>
-      </c>
-      <c r="P42" t="n">
-        <v>0</v>
-      </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>14.13810794367885</v>
       </c>
       <c r="R42" t="n">
         <v>0</v>
@@ -38140,25 +38140,25 @@
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>0</v>
+        <v>127.0000000000587</v>
       </c>
       <c r="K45" t="n">
         <v>127.0000000000587</v>
       </c>
       <c r="L45" t="n">
-        <v>77.59246726220807</v>
+        <v>0</v>
       </c>
       <c r="M45" t="n">
         <v>0</v>
       </c>
       <c r="N45" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" t="n">
+        <v>57.54405296337715</v>
+      </c>
+      <c r="P45" t="n">
         <v>127.0000000000587</v>
-      </c>
-      <c r="O45" t="n">
-        <v>106.9515857012278</v>
-      </c>
-      <c r="P45" t="n">
-        <v>0</v>
       </c>
       <c r="Q45" t="n">
         <v>64.32463390563181</v>
